--- a/outputs/connected_spreadsheet_test/connected_sensory_threshold_gate_test.xlsx
+++ b/outputs/connected_spreadsheet_test/connected_sensory_threshold_gate_test.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Compact View" sheetId="1" r:id="R3f109bbdcbca44b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Sensory Input" sheetId="2" r:id="R270dea3322eb461e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02a n" sheetId="3" r:id="Rb5561c5c25564fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02b n^-1" sheetId="4" r:id="Re69728b974054630"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02c n^-2" sheetId="5" r:id="Ra78c589438564c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mind Knobs" sheetId="6" r:id="Re78f722190d64c65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Resource Body" sheetId="7" r:id="R799969a4246245ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Gate Output" sheetId="8" r:id="Rcfed1a7c75834d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Mode Presets" sheetId="9" r:id="Rda0cd7c007c146f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Summary" sheetId="10" r:id="R3b5443efcc714d7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Compact View" sheetId="1" r:id="R6a3090b5747b4818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Sensory Input" sheetId="2" r:id="R88a4ae9b126b4e22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02a n" sheetId="3" r:id="R779391b3d0de454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02b n^-1" sheetId="4" r:id="R51f43b36323c40d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02c n^-2" sheetId="5" r:id="R7c6b90bfcd2b4e81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mind Knobs" sheetId="6" r:id="R672d12be64904a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Resource Body" sheetId="7" r:id="Rf5875ae5b50d425a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Gate Output" sheetId="8" r:id="Ra9837118a1194ce0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Habit Efficiency" sheetId="9" r:id="R4243966080ff4af4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Mode Presets" sheetId="10" r:id="R411eeffef5dd4bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Summary" sheetId="11" r:id="R0f391dc3bfe44157"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -117,7 +118,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -131,6 +132,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
@@ -21816,58 +21818,729 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="4.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="6.440000057220459" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="19.5" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>07 Summary</x:v>
+        <x:v>07 Mode Presets</x:v>
       </x:c>
       <x:c r="B1" s="4" t="str">
-        <x:v>07 Summary</x:v>
+        <x:v>07 Mode Presets</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
-        <x:v>07 Summary</x:v>
+        <x:v>07 Mode Presets</x:v>
       </x:c>
       <x:c r="D1" s="4" t="str">
-        <x:v>07 Summary</x:v>
+        <x:v>07 Mode Presets</x:v>
       </x:c>
       <x:c r="E1" s="4" t="str">
-        <x:v>07 Summary</x:v>
+        <x:v>07 Mode Presets</x:v>
       </x:c>
       <x:c r="F1" s="4" t="str">
-        <x:v>07 Summary</x:v>
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="K1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="L1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="M1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="N1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="O1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="P1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="Q1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="R1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="S1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
+      </x:c>
+      <x:c r="T1" s="4" t="str">
+        <x:v>07 Mode Presets</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Compact sample-level numeric summary.</x:v>
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Compact sample-level numeric summary.</x:v>
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Compact sample-level numeric summary.</x:v>
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Compact sample-level numeric summary.</x:v>
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Compact sample-level numeric summary.</x:v>
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Compact sample-level numeric summary.</x:v>
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="P2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="Q2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="R2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="S2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+      <x:c r="T2" s="6" t="str">
+        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>mode</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>nov</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>em</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="str">
+        <x:v>win</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>res</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="str">
+        <x:v>cur_bud</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="str">
+        <x:v>inner</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="str">
+        <x:v>curiosity</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="str">
+        <x:v>emwin</x:v>
+      </x:c>
+      <x:c r="K5" s="10" t="str">
+        <x:v>xw</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="str">
+        <x:v>aw</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>prom</x:v>
+      </x:c>
+      <x:c r="N5" s="10" t="str">
+        <x:v>eff</x:v>
+      </x:c>
+      <x:c r="O5" s="10" t="str">
+        <x:v>rep</x:v>
+      </x:c>
+      <x:c r="P5" s="10" t="str">
+        <x:v>conf</x:v>
+      </x:c>
+      <x:c r="Q5" s="10" t="str">
+        <x:v>fail</x:v>
+      </x:c>
+      <x:c r="R5" s="10" t="str">
+        <x:v>partial</x:v>
+      </x:c>
+      <x:c r="S5" s="10" t="str">
+        <x:v>audit</x:v>
+      </x:c>
+      <x:c r="T5" s="11" t="str">
+        <x:v>mismatch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>calm</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K6" s="12" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="L6" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="M6" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="N6" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="O6" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P6" s="12" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="Q6" s="12" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="R6" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S6" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T6" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>curious</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="J7" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L7" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="N7" s="12" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="O7" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P7" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="Q7" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="R7" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S7" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T7" s="12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>focused</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="J8" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K8" s="12" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="L8" s="12" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="M8" s="12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="N8" s="12" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O8" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P8" s="12" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="Q8" s="12" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="R8" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S8" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T8" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>strained</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J9" s="12" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K9" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="L9" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="M9" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="N9" s="12" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="O9" s="12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P9" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="Q9" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="R9" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S9" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T9" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>danger</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K10" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="L10" s="12" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="M10" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="N10" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O10" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P10" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="Q10" s="12" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="R10" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S10" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T10" s="12" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>recovery</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K11" s="12" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L11" s="12" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="M11" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="N11" s="12" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="O11" s="12" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P11" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="Q11" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="R11" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S11" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T11" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:T1"/>
+    <x:mergeCell ref="A2:T2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="6.21999979019165" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="6.21999979019165" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="K1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="L1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="M1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="N1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="O1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="P1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="Q1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+      <x:c r="R1" s="4" t="str">
+        <x:v>08 Summary</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="P2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="Q2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
+      </x:c>
+      <x:c r="R2" s="6" t="str">
+        <x:v>Compact sample-level numeric summary with resource, habit, and efficiency outputs.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -21904,8 +22577,26 @@
       <x:c r="K5" s="10" t="str">
         <x:v>up</x:v>
       </x:c>
-      <x:c r="L5" s="11" t="str">
+      <x:c r="L5" s="10" t="str">
         <x:v>res</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>homeo</x:v>
+      </x:c>
+      <x:c r="N5" s="10" t="str">
+        <x:v>eff</x:v>
+      </x:c>
+      <x:c r="O5" s="10" t="str">
+        <x:v>handoff</x:v>
+      </x:c>
+      <x:c r="P5" s="10" t="str">
+        <x:v>partial</x:v>
+      </x:c>
+      <x:c r="Q5" s="10" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="R5" s="11" t="str">
+        <x:v>audit</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -21955,6 +22646,30 @@
       </x:c>
       <x:c r="L6" s="12" t="n">
         <x:f>'04 Resource Body'!$B$10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A6)</x:f>
+        <x:v>0.94621875</x:v>
+      </x:c>
+      <x:c r="O6" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -22007,6 +22722,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M7" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N7" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A7)</x:f>
+        <x:v>0.94621875</x:v>
+      </x:c>
+      <x:c r="O7" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A7)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A7)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A7)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A7)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
@@ -22057,6 +22796,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M8" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N8" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A8)</x:f>
+        <x:v>0.9329375</x:v>
+      </x:c>
+      <x:c r="O8" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A8)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A8)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A8)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A8)</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="n">
@@ -22107,6 +22870,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M9" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N9" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A9)</x:f>
+        <x:v>0.9871562500000001</x:v>
+      </x:c>
+      <x:c r="O9" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A9)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A9)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q9" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A9)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A9)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="n">
@@ -22157,6 +22944,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M10" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N10" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A10)</x:f>
+        <x:v>0.98546875</x:v>
+      </x:c>
+      <x:c r="O10" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A10)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A10)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q10" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A10)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A10)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="n">
@@ -22207,6 +23018,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M11" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N11" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A11)</x:f>
+        <x:v>0.99390625</x:v>
+      </x:c>
+      <x:c r="O11" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A11)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A11)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q11" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A11)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A11)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="n">
@@ -22257,6 +23092,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M12" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N12" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A12)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O12" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A12)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P12" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A12)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A12)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R12" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A12)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="n">
@@ -22307,6 +23166,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M13" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N13" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A13)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O13" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A13)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A13)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q13" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A13)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A13)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="n">
@@ -22357,6 +23240,30 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M14" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N14" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A14)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O14" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A14)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P14" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A14)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A14)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R14" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A14)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="n">
@@ -22407,11 +23314,35 @@
         <x:f>'04 Resource Body'!$B$10</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="M15" s="12" t="n">
+        <x:f>'04 Resource Body'!$D$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N15" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$M$6:$M$15,A15)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O15" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$I$6:$I$15,A15)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P15" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$J$6:$J$15,A15)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$K$6:$K$15,A15)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R15" s="12" t="n">
+        <x:f>INDEX('06 Habit Efficiency'!$L$6:$L$15,A15)</x:f>
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A1:R1"/>
+    <x:mergeCell ref="A2:R2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -43797,11 +44728,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="4.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.559999942779541" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.559999942779541" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="19.5" customHeight="1">
@@ -43823,19 +44754,19 @@
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Editable control surface. v drives formulas. p shows the selected mode preset.</x:v>
+        <x:v>Editable control surface. v drives formulas. p shows the selected curious-mode defaults.</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Editable control surface. v drives formulas. p shows the selected mode preset.</x:v>
+        <x:v>Editable control surface. v drives formulas. p shows the selected curious-mode defaults.</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Editable control surface. v drives formulas. p shows the selected mode preset.</x:v>
+        <x:v>Editable control surface. v drives formulas. p shows the selected curious-mode defaults.</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Editable control surface. v drives formulas. p shows the selected mode preset.</x:v>
+        <x:v>Editable control surface. v drives formulas. p shows the selected curious-mode defaults.</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Editable control surface. v drives formulas. p shows the selected mode preset.</x:v>
+        <x:v>Editable control surface. v drives formulas. p shows the selected curious-mode defaults.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -43878,7 +44809,7 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="C7" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$C$6:$C$11,$B$6)</x:f>
+        <x:f>INDEX('07 Mode Presets'!$C$6:$C$11,$B$6)</x:f>
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="D7" t="n">
@@ -43896,7 +44827,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="C8" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$D$6:$D$11,$B$6)</x:f>
+        <x:f>INDEX('07 Mode Presets'!$D$6:$D$11,$B$6)</x:f>
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="D8" t="n">
@@ -43914,7 +44845,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$E$6:$E$11,$B$6)</x:f>
+        <x:f>INDEX('07 Mode Presets'!$E$6:$E$11,$B$6)</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="D9" t="n">
@@ -43932,7 +44863,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="C10" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$F$6:$F$11,$B$6)</x:f>
+        <x:f>INDEX('07 Mode Presets'!$F$6:$F$11,$B$6)</x:f>
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="D10" t="n">
@@ -43950,7 +44881,7 @@
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="C11" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$G$6:$G$11,$B$6)</x:f>
+        <x:f>INDEX('07 Mode Presets'!$G$6:$G$11,$B$6)</x:f>
         <x:v>0.7</x:v>
       </x:c>
       <x:c r="D11" t="n">
@@ -43962,14 +44893,14 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>in_attn</x:v>
+        <x:v>inner_build</x:v>
       </x:c>
       <x:c r="B12" s="12" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C12" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$H$6:$H$11,$B$6)</x:f>
-        <x:v>0.8</x:v>
+        <x:f>INDEX('07 Mode Presets'!$H$6:$H$11,$B$6)</x:f>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>0</x:v>
@@ -43980,15 +44911,14 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
-        <x:v>out_attn</x:v>
+        <x:v>curiosity</x:v>
       </x:c>
       <x:c r="B13" s="12" t="n">
-        <x:f>1-B12</x:f>
-        <x:v>0.19999999999999996</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="C13" s="12" t="n">
-        <x:f>1-C12</x:f>
-        <x:v>0.19999999999999996</x:v>
+        <x:f>INDEX('07 Mode Presets'!$I$6:$I$11,$B$6)</x:f>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>0</x:v>
@@ -43999,32 +44929,34 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
-        <x:v>em_win</x:v>
+        <x:v>unassigned</x:v>
       </x:c>
       <x:c r="B14" s="12" t="n">
-        <x:v>10</x:v>
+        <x:f>MAX(0,1-B12-B13)</x:f>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="C14" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$I$6:$I$11,$B$6)</x:f>
-        <x:v>10</x:v>
+        <x:f>MAX(0,1-C12-C13)</x:f>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
-        <x:v>x_w</x:v>
+        <x:v>out_attn</x:v>
       </x:c>
       <x:c r="B15" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:f>B14</x:f>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="C15" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$J$6:$J$11,$B$6)</x:f>
-        <x:v>0.5</x:v>
+        <x:f>C14</x:f>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:v>0</x:v>
@@ -44035,37 +44967,199 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>a_w</x:v>
+        <x:v>em_win</x:v>
       </x:c>
       <x:c r="B16" s="12" t="n">
-        <x:v>0.7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C16" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$K$6:$K$11,$B$6)</x:f>
-        <x:v>0.7</x:v>
+        <x:f>INDEX('07 Mode Presets'!$J$6:$J$11,$B$6)</x:f>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D16" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
+        <x:v>x_w</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C17" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$K$6:$K$11,$B$6)</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>a_w</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="C18" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$L$6:$L$11,$B$6)</x:f>
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
         <x:v>prom_base</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="n">
+      <x:c r="B19" s="12" t="n">
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="n">
-        <x:f>INDEX('06 Mode Presets'!$L$6:$L$11,$B$6)</x:f>
+      <x:c r="C19" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$M$6:$M$11,$B$6)</x:f>
         <x:v>0.55</x:v>
       </x:c>
-      <x:c r="D17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" t="n">
+      <x:c r="D19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>eff_drive</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="C20" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$N$6:$N$11,$B$6)</x:f>
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>habit_rep</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C21" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$O$6:$O$11,$B$6)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>habit_conf</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="C22" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$P$6:$P$11,$B$6)</x:f>
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>fail_tol</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="C23" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$Q$6:$Q$11,$B$6)</x:f>
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>partial_ok</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$R$6:$R$11,$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>audit_compact</x:v>
+      </x:c>
+      <x:c r="B25" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C25" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$S$6:$S$11,$B$6)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>mismatch_imp</x:v>
+      </x:c>
+      <x:c r="B26" s="12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="C26" s="12" t="n">
+        <x:f>INDEX('07 Mode Presets'!$T$6:$T$11,$B$6)</x:f>
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -44082,12 +45176,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.440000057220459" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="19.5" customHeight="1">
@@ -44235,22 +45329,37 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C10" s="12"/>
-      <x:c r="D10" s="12"/>
-      <x:c r="E10" s="12"/>
-      <x:c r="F10" s="12"/>
+      <x:c r="D10" s="13" t="str">
+        <x:v>homeo</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>danger</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="str">
+        <x:v>eff</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
         <x:v>cur_eff</x:v>
       </x:c>
       <x:c r="B11" s="12" t="n">
-        <x:f>MAX(0,'03 Mind Knobs'!$B$11*(1-B10*'03 Mind Knobs'!$B$10))</x:f>
-        <x:v>0.7</x:v>
+        <x:f>MAX(0,'03 Mind Knobs'!$B$13*(1-B10*'03 Mind Knobs'!$B$10))</x:f>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="C11" s="12"/>
-      <x:c r="D11" s="12"/>
-      <x:c r="E11" s="12"/>
-      <x:c r="F11" s="12"/>
+      <x:c r="D11" s="12" t="n">
+        <x:f>MAX(0,1-B10)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="n">
+        <x:f>--(MAX(B6:B8)&gt;=C6)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="n">
+        <x:f>MIN(1,'03 Mind Knobs'!$B$20+(B10*0.15))</x:f>
+        <x:v>0.85</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="12"/>
@@ -44263,13 +45372,13 @@
       <x:c r="A13" s="9" t="str">
         <x:v>sense</x:v>
       </x:c>
-      <x:c r="B13" s="13" t="str">
+      <x:c r="B13" s="14" t="str">
         <x:v>gb</x:v>
       </x:c>
-      <x:c r="C13" s="13" t="str">
+      <x:c r="C13" s="14" t="str">
         <x:v>demand</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="str">
+      <x:c r="D13" s="15" t="str">
         <x:v>fill</x:v>
       </x:c>
       <x:c r="E13" s="12"/>
@@ -44386,9 +45495,31 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C20" s="12"/>
-      <x:c r="D20" s="12"/>
-      <x:c r="E20" s="12"/>
-      <x:c r="F20" s="12"/>
+      <x:c r="D20" s="13" t="str">
+        <x:v>avoid</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>comp</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="str">
+        <x:v>inner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="B21" s="12"/>
+      <x:c r="C21" s="12"/>
+      <x:c r="D21" s="12" t="n">
+        <x:f>MIN(1,F11*0.65+(1-D11)*0.35)</x:f>
+        <x:v>0.5525</x:v>
+      </x:c>
+      <x:c r="E21" s="12" t="n">
+        <x:f>MIN(1,B10*0.55+F11*0.45)</x:f>
+        <x:v>0.3825</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="n">
+        <x:f>MAX(0,'03 Mind Knobs'!$B$12-(B10*0.25)-(E11*0.30))</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -44575,11 +45706,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" t="n">
-        <x:f>--(MIN(1,C6+D6+(E6*'03 Mind Knobs'!$B$15)+(F6*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F6))&gt;=MAX(0.15,0.35+(G6*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C6+D6+(E6*'03 Mind Knobs'!$B$17)+(F6*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F6))&gt;=MAX(0.15,0.35+(G6*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" t="n">
-        <x:f>--(MIN(1,C6+D6+(E6*'03 Mind Knobs'!$B$15)+(F6*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F6))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G6*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C6+D6+(E6*'03 Mind Knobs'!$B$17)+(F6*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F6))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G6*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K6" t="n">
@@ -44587,7 +45718,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L6" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A6,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B6-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B6))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" t="n">
@@ -44629,11 +45760,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I7" t="n">
-        <x:f>--(MIN(1,C7+D7+(E7*'03 Mind Knobs'!$B$15)+(F7*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F7))&gt;=MAX(0.15,0.35+(G7*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C7+D7+(E7*'03 Mind Knobs'!$B$17)+(F7*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F7))&gt;=MAX(0.15,0.35+(G7*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" t="n">
-        <x:f>--(MIN(1,C7+D7+(E7*'03 Mind Knobs'!$B$15)+(F7*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F7))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G7*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C7+D7+(E7*'03 Mind Knobs'!$B$17)+(F7*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F7))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G7*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K7" t="n">
@@ -44641,7 +45772,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L7" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A7,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B7-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B7))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M7" t="n">
@@ -44683,11 +45814,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" t="n">
-        <x:f>--(MIN(1,C8+D8+(E8*'03 Mind Knobs'!$B$15)+(F8*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F8))&gt;=MAX(0.15,0.35+(G8*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C8+D8+(E8*'03 Mind Knobs'!$B$17)+(F8*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F8))&gt;=MAX(0.15,0.35+(G8*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" t="n">
-        <x:f>--(MIN(1,C8+D8+(E8*'03 Mind Knobs'!$B$15)+(F8*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F8))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G8*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C8+D8+(E8*'03 Mind Knobs'!$B$17)+(F8*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F8))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G8*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" t="n">
@@ -44695,7 +45826,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L8" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A8,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B8-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B8))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" t="n">
@@ -44737,11 +45868,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I9" t="n">
-        <x:f>--(MIN(1,C9+D9+(E9*'03 Mind Knobs'!$B$15)+(F9*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F9))&gt;=MAX(0.15,0.35+(G9*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C9+D9+(E9*'03 Mind Knobs'!$B$17)+(F9*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F9))&gt;=MAX(0.15,0.35+(G9*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" t="n">
-        <x:f>--(MIN(1,C9+D9+(E9*'03 Mind Knobs'!$B$15)+(F9*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F9))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G9*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C9+D9+(E9*'03 Mind Knobs'!$B$17)+(F9*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F9))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G9*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K9" t="n">
@@ -44749,7 +45880,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L9" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A9,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B9-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B9))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" t="n">
@@ -44791,11 +45922,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I10" t="n">
-        <x:f>--(MIN(1,C10+D10+(E10*'03 Mind Knobs'!$B$15)+(F10*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F10))&gt;=MAX(0.15,0.35+(G10*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C10+D10+(E10*'03 Mind Knobs'!$B$17)+(F10*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F10))&gt;=MAX(0.15,0.35+(G10*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" t="n">
-        <x:f>--(MIN(1,C10+D10+(E10*'03 Mind Knobs'!$B$15)+(F10*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F10))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G10*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C10+D10+(E10*'03 Mind Knobs'!$B$17)+(F10*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F10))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G10*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K10" t="n">
@@ -44803,7 +45934,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L10" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A10,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B10-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B10))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M10" t="n">
@@ -44845,11 +45976,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" t="n">
-        <x:f>--(MIN(1,C11+D11+(E11*'03 Mind Knobs'!$B$15)+(F11*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F11))&gt;=MAX(0.15,0.35+(G11*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C11+D11+(E11*'03 Mind Knobs'!$B$17)+(F11*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F11))&gt;=MAX(0.15,0.35+(G11*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" t="n">
-        <x:f>--(MIN(1,C11+D11+(E11*'03 Mind Knobs'!$B$15)+(F11*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F11))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G11*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C11+D11+(E11*'03 Mind Knobs'!$B$17)+(F11*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F11))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G11*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K11" t="n">
@@ -44857,7 +45988,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L11" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A11,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B11-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B11))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" t="n">
@@ -44899,11 +46030,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I12" t="n">
-        <x:f>--(MIN(1,C12+D12+(E12*'03 Mind Knobs'!$B$15)+(F12*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F12))&gt;=MAX(0.15,0.35+(G12*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C12+D12+(E12*'03 Mind Knobs'!$B$17)+(F12*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F12))&gt;=MAX(0.15,0.35+(G12*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" t="n">
-        <x:f>--(MIN(1,C12+D12+(E12*'03 Mind Knobs'!$B$15)+(F12*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F12))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G12*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C12+D12+(E12*'03 Mind Knobs'!$B$17)+(F12*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F12))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G12*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K12" t="n">
@@ -44911,7 +46042,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L12" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A12,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B12-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B12))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" t="n">
@@ -44953,11 +46084,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" t="n">
-        <x:f>--(MIN(1,C13+D13+(E13*'03 Mind Knobs'!$B$15)+(F13*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F13))&gt;=MAX(0.15,0.35+(G13*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C13+D13+(E13*'03 Mind Knobs'!$B$17)+(F13*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F13))&gt;=MAX(0.15,0.35+(G13*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J13" t="n">
-        <x:f>--(MIN(1,C13+D13+(E13*'03 Mind Knobs'!$B$15)+(F13*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F13))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G13*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C13+D13+(E13*'03 Mind Knobs'!$B$17)+(F13*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F13))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G13*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" t="n">
@@ -44965,7 +46096,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L13" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A13,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B13-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B13))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" t="n">
@@ -45007,11 +46138,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" t="n">
-        <x:f>--(MIN(1,C14+D14+(E14*'03 Mind Knobs'!$B$15)+(F14*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F14))&gt;=MAX(0.15,0.35+(G14*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C14+D14+(E14*'03 Mind Knobs'!$B$17)+(F14*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F14))&gt;=MAX(0.15,0.35+(G14*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" t="n">
-        <x:f>--(MIN(1,C14+D14+(E14*'03 Mind Knobs'!$B$15)+(F14*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F14))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G14*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C14+D14+(E14*'03 Mind Knobs'!$B$17)+(F14*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F14))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G14*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K14" t="n">
@@ -45019,7 +46150,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L14" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A14,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B14-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B14))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" t="n">
@@ -45061,11 +46192,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" t="n">
-        <x:f>--(MIN(1,C15+D15+(E15*'03 Mind Knobs'!$B$15)+(F15*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F15))&gt;=MAX(0.15,0.35+(G15*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C15+D15+(E15*'03 Mind Knobs'!$B$17)+(F15*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F15))&gt;=MAX(0.15,0.35+(G15*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" t="n">
-        <x:f>--(MIN(1,C15+D15+(E15*'03 Mind Knobs'!$B$15)+(F15*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F15))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G15*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C15+D15+(E15*'03 Mind Knobs'!$B$17)+(F15*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F15))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G15*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K15" t="n">
@@ -45073,7 +46204,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L15" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A15,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B15-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B15))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" t="n">
@@ -45115,11 +46246,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" t="n">
-        <x:f>--(MIN(1,C16+D16+(E16*'03 Mind Knobs'!$B$15)+(F16*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F16))&gt;=MAX(0.15,0.35+(G16*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C16+D16+(E16*'03 Mind Knobs'!$B$17)+(F16*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F16))&gt;=MAX(0.15,0.35+(G16*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" t="n">
-        <x:f>--(MIN(1,C16+D16+(E16*'03 Mind Knobs'!$B$15)+(F16*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F16))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G16*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C16+D16+(E16*'03 Mind Knobs'!$B$17)+(F16*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F16))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G16*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K16" t="n">
@@ -45127,7 +46258,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L16" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A16,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B16-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B16))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" t="n">
@@ -45169,11 +46300,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" t="n">
-        <x:f>--(MIN(1,C17+D17+(E17*'03 Mind Knobs'!$B$15)+(F17*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F17))&gt;=MAX(0.15,0.35+(G17*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C17+D17+(E17*'03 Mind Knobs'!$B$17)+(F17*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F17))&gt;=MAX(0.15,0.35+(G17*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" t="n">
-        <x:f>--(MIN(1,C17+D17+(E17*'03 Mind Knobs'!$B$15)+(F17*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F17))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G17*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C17+D17+(E17*'03 Mind Knobs'!$B$17)+(F17*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F17))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G17*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" t="n">
@@ -45181,7 +46312,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L17" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A17,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B17-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B17))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" t="n">
@@ -45223,11 +46354,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I18" t="n">
-        <x:f>--(MIN(1,C18+D18+(E18*'03 Mind Knobs'!$B$15)+(F18*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F18))&gt;=MAX(0.15,0.35+(G18*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C18+D18+(E18*'03 Mind Knobs'!$B$17)+(F18*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F18))&gt;=MAX(0.15,0.35+(G18*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J18" t="n">
-        <x:f>--(MIN(1,C18+D18+(E18*'03 Mind Knobs'!$B$15)+(F18*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F18))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G18*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C18+D18+(E18*'03 Mind Knobs'!$B$17)+(F18*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F18))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G18*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K18" t="n">
@@ -45235,7 +46366,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L18" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A18,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B18-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B18))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M18" t="n">
@@ -45277,11 +46408,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" t="n">
-        <x:f>--(MIN(1,C19+D19+(E19*'03 Mind Knobs'!$B$15)+(F19*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F19))&gt;=MAX(0.15,0.35+(G19*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C19+D19+(E19*'03 Mind Knobs'!$B$17)+(F19*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F19))&gt;=MAX(0.15,0.35+(G19*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J19" t="n">
-        <x:f>--(MIN(1,C19+D19+(E19*'03 Mind Knobs'!$B$15)+(F19*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F19))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G19*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C19+D19+(E19*'03 Mind Knobs'!$B$17)+(F19*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F19))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G19*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K19" t="n">
@@ -45289,7 +46420,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L19" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A19,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B19-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B19))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M19" t="n">
@@ -45331,11 +46462,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" t="n">
-        <x:f>--(MIN(1,C20+D20+(E20*'03 Mind Knobs'!$B$15)+(F20*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F20))&gt;=MAX(0.15,0.35+(G20*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C20+D20+(E20*'03 Mind Knobs'!$B$17)+(F20*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F20))&gt;=MAX(0.15,0.35+(G20*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J20" t="n">
-        <x:f>--(MIN(1,C20+D20+(E20*'03 Mind Knobs'!$B$15)+(F20*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F20))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G20*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C20+D20+(E20*'03 Mind Knobs'!$B$17)+(F20*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F20))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G20*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K20" t="n">
@@ -45343,7 +46474,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L20" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A20,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B20-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B20))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M20" t="n">
@@ -45385,11 +46516,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" t="n">
-        <x:f>--(MIN(1,C21+D21+(E21*'03 Mind Knobs'!$B$15)+(F21*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F21))&gt;=MAX(0.15,0.35+(G21*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C21+D21+(E21*'03 Mind Knobs'!$B$17)+(F21*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F21))&gt;=MAX(0.15,0.35+(G21*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J21" t="n">
-        <x:f>--(MIN(1,C21+D21+(E21*'03 Mind Knobs'!$B$15)+(F21*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F21))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G21*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C21+D21+(E21*'03 Mind Knobs'!$B$17)+(F21*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F21))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G21*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K21" t="n">
@@ -45397,7 +46528,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L21" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A21,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B21-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B21))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M21" t="n">
@@ -45439,11 +46570,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" t="n">
-        <x:f>--(MIN(1,C22+D22+(E22*'03 Mind Knobs'!$B$15)+(F22*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F22))&gt;=MAX(0.15,0.35+(G22*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C22+D22+(E22*'03 Mind Knobs'!$B$17)+(F22*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F22))&gt;=MAX(0.15,0.35+(G22*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" t="n">
-        <x:f>--(MIN(1,C22+D22+(E22*'03 Mind Knobs'!$B$15)+(F22*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F22))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G22*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C22+D22+(E22*'03 Mind Knobs'!$B$17)+(F22*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F22))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G22*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K22" t="n">
@@ -45451,7 +46582,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L22" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A22,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B22-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B22))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M22" t="n">
@@ -45493,11 +46624,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" t="n">
-        <x:f>--(MIN(1,C23+D23+(E23*'03 Mind Knobs'!$B$15)+(F23*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F23))&gt;=MAX(0.15,0.35+(G23*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C23+D23+(E23*'03 Mind Knobs'!$B$17)+(F23*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F23))&gt;=MAX(0.15,0.35+(G23*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" t="n">
-        <x:f>--(MIN(1,C23+D23+(E23*'03 Mind Knobs'!$B$15)+(F23*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F23))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G23*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C23+D23+(E23*'03 Mind Knobs'!$B$17)+(F23*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F23))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G23*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K23" t="n">
@@ -45505,7 +46636,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L23" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A23,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B23-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B23))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M23" t="n">
@@ -45547,11 +46678,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" t="n">
-        <x:f>--(MIN(1,C24+D24+(E24*'03 Mind Knobs'!$B$15)+(F24*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F24))&gt;=MAX(0.15,0.35+(G24*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C24+D24+(E24*'03 Mind Knobs'!$B$17)+(F24*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F24))&gt;=MAX(0.15,0.35+(G24*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J24" t="n">
-        <x:f>--(MIN(1,C24+D24+(E24*'03 Mind Knobs'!$B$15)+(F24*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F24))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G24*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C24+D24+(E24*'03 Mind Knobs'!$B$17)+(F24*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F24))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G24*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K24" t="n">
@@ -45559,7 +46690,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L24" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A24,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B24-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B24))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M24" t="n">
@@ -45601,11 +46732,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I25" t="n">
-        <x:f>--(MIN(1,C25+D25+(E25*'03 Mind Knobs'!$B$15)+(F25*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F25))&gt;=MAX(0.15,0.35+(G25*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C25+D25+(E25*'03 Mind Knobs'!$B$17)+(F25*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F25))&gt;=MAX(0.15,0.35+(G25*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J25" t="n">
-        <x:f>--(MIN(1,C25+D25+(E25*'03 Mind Knobs'!$B$15)+(F25*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F25))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G25*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C25+D25+(E25*'03 Mind Knobs'!$B$17)+(F25*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F25))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G25*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K25" t="n">
@@ -45613,7 +46744,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L25" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A25,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B25-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B25))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M25" t="n">
@@ -45655,11 +46786,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I26" t="n">
-        <x:f>--(MIN(1,C26+D26+(E26*'03 Mind Knobs'!$B$15)+(F26*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F26))&gt;=MAX(0.15,0.35+(G26*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C26+D26+(E26*'03 Mind Knobs'!$B$17)+(F26*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F26))&gt;=MAX(0.15,0.35+(G26*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" t="n">
-        <x:f>--(MIN(1,C26+D26+(E26*'03 Mind Knobs'!$B$15)+(F26*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F26))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G26*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C26+D26+(E26*'03 Mind Knobs'!$B$17)+(F26*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F26))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G26*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K26" t="n">
@@ -45667,7 +46798,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L26" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A26,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B26-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B26))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M26" t="n">
@@ -45709,11 +46840,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" t="n">
-        <x:f>--(MIN(1,C27+D27+(E27*'03 Mind Knobs'!$B$15)+(F27*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F27))&gt;=MAX(0.15,0.35+(G27*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C27+D27+(E27*'03 Mind Knobs'!$B$17)+(F27*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F27))&gt;=MAX(0.15,0.35+(G27*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" t="n">
-        <x:f>--(MIN(1,C27+D27+(E27*'03 Mind Knobs'!$B$15)+(F27*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F27))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G27*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C27+D27+(E27*'03 Mind Knobs'!$B$17)+(F27*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F27))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G27*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K27" t="n">
@@ -45721,7 +46852,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L27" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A27,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B27-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B27))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M27" t="n">
@@ -45763,11 +46894,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I28" t="n">
-        <x:f>--(MIN(1,C28+D28+(E28*'03 Mind Knobs'!$B$15)+(F28*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F28))&gt;=MAX(0.15,0.35+(G28*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C28+D28+(E28*'03 Mind Knobs'!$B$17)+(F28*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F28))&gt;=MAX(0.15,0.35+(G28*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" t="n">
-        <x:f>--(MIN(1,C28+D28+(E28*'03 Mind Knobs'!$B$15)+(F28*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F28))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G28*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C28+D28+(E28*'03 Mind Knobs'!$B$17)+(F28*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F28))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G28*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K28" t="n">
@@ -45775,7 +46906,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L28" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A28,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B28-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B28))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M28" t="n">
@@ -45817,11 +46948,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" t="n">
-        <x:f>--(MIN(1,C29+D29+(E29*'03 Mind Knobs'!$B$15)+(F29*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F29))&gt;=MAX(0.15,0.35+(G29*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C29+D29+(E29*'03 Mind Knobs'!$B$17)+(F29*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F29))&gt;=MAX(0.15,0.35+(G29*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J29" t="n">
-        <x:f>--(MIN(1,C29+D29+(E29*'03 Mind Knobs'!$B$15)+(F29*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F29))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G29*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C29+D29+(E29*'03 Mind Knobs'!$B$17)+(F29*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F29))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G29*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K29" t="n">
@@ -45829,7 +46960,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L29" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A29,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B29-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B29))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M29" t="n">
@@ -45871,11 +47002,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" t="n">
-        <x:f>--(MIN(1,C30+D30+(E30*'03 Mind Knobs'!$B$15)+(F30*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F30))&gt;=MAX(0.15,0.35+(G30*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C30+D30+(E30*'03 Mind Knobs'!$B$17)+(F30*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F30))&gt;=MAX(0.15,0.35+(G30*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" t="n">
-        <x:f>--(MIN(1,C30+D30+(E30*'03 Mind Knobs'!$B$15)+(F30*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F30))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G30*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C30+D30+(E30*'03 Mind Knobs'!$B$17)+(F30*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F30))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G30*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K30" t="n">
@@ -45883,7 +47014,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L30" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A30,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B30-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B30))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M30" t="n">
@@ -45925,11 +47056,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:f>--(MIN(1,C31+D31+(E31*'03 Mind Knobs'!$B$15)+(F31*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F31))&gt;=MAX(0.15,0.35+(G31*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C31+D31+(E31*'03 Mind Knobs'!$B$17)+(F31*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F31))&gt;=MAX(0.15,0.35+(G31*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J31" t="n">
-        <x:f>--(MIN(1,C31+D31+(E31*'03 Mind Knobs'!$B$15)+(F31*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F31))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G31*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C31+D31+(E31*'03 Mind Knobs'!$B$17)+(F31*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F31))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G31*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K31" t="n">
@@ -45937,7 +47068,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L31" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A31,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B31-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B31))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M31" t="n">
@@ -45979,11 +47110,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I32" t="n">
-        <x:f>--(MIN(1,C32+D32+(E32*'03 Mind Knobs'!$B$15)+(F32*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F32))&gt;=MAX(0.15,0.35+(G32*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C32+D32+(E32*'03 Mind Knobs'!$B$17)+(F32*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F32))&gt;=MAX(0.15,0.35+(G32*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" t="n">
-        <x:f>--(MIN(1,C32+D32+(E32*'03 Mind Knobs'!$B$15)+(F32*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F32))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G32*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C32+D32+(E32*'03 Mind Knobs'!$B$17)+(F32*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F32))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G32*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K32" t="n">
@@ -45991,7 +47122,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L32" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A32,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B32-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B32))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M32" t="n">
@@ -46033,11 +47164,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I33" t="n">
-        <x:f>--(MIN(1,C33+D33+(E33*'03 Mind Knobs'!$B$15)+(F33*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F33))&gt;=MAX(0.15,0.35+(G33*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C33+D33+(E33*'03 Mind Knobs'!$B$17)+(F33*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F33))&gt;=MAX(0.15,0.35+(G33*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" t="n">
-        <x:f>--(MIN(1,C33+D33+(E33*'03 Mind Knobs'!$B$15)+(F33*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F33))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G33*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C33+D33+(E33*'03 Mind Knobs'!$B$17)+(F33*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F33))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G33*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K33" t="n">
@@ -46045,7 +47176,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L33" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A33,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B33-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B33))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M33" t="n">
@@ -46087,11 +47218,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I34" t="n">
-        <x:f>--(MIN(1,C34+D34+(E34*'03 Mind Knobs'!$B$15)+(F34*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F34))&gt;=MAX(0.15,0.35+(G34*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C34+D34+(E34*'03 Mind Knobs'!$B$17)+(F34*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F34))&gt;=MAX(0.15,0.35+(G34*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" t="n">
-        <x:f>--(MIN(1,C34+D34+(E34*'03 Mind Knobs'!$B$15)+(F34*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F34))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G34*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C34+D34+(E34*'03 Mind Knobs'!$B$17)+(F34*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F34))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G34*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K34" t="n">
@@ -46099,7 +47230,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L34" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A34,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B34-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B34))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M34" t="n">
@@ -46141,11 +47272,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" t="n">
-        <x:f>--(MIN(1,C35+D35+(E35*'03 Mind Knobs'!$B$15)+(F35*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F35))&gt;=MAX(0.15,0.35+(G35*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C35+D35+(E35*'03 Mind Knobs'!$B$17)+(F35*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F35))&gt;=MAX(0.15,0.35+(G35*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" t="n">
-        <x:f>--(MIN(1,C35+D35+(E35*'03 Mind Knobs'!$B$15)+(F35*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F35))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G35*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C35+D35+(E35*'03 Mind Knobs'!$B$17)+(F35*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F35))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G35*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K35" t="n">
@@ -46153,7 +47284,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L35" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A35,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B35-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B35))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M35" t="n">
@@ -46195,11 +47326,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I36" t="n">
-        <x:f>--(MIN(1,C36+D36+(E36*'03 Mind Knobs'!$B$15)+(F36*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F36))&gt;=MAX(0.15,0.35+(G36*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C36+D36+(E36*'03 Mind Knobs'!$B$17)+(F36*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F36))&gt;=MAX(0.15,0.35+(G36*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J36" t="n">
-        <x:f>--(MIN(1,C36+D36+(E36*'03 Mind Knobs'!$B$15)+(F36*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F36))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G36*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C36+D36+(E36*'03 Mind Knobs'!$B$17)+(F36*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F36))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G36*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K36" t="n">
@@ -46207,7 +47338,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L36" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A36,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B36-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B36))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M36" t="n">
@@ -46249,11 +47380,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I37" t="n">
-        <x:f>--(MIN(1,C37+D37+(E37*'03 Mind Knobs'!$B$15)+(F37*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F37))&gt;=MAX(0.15,0.35+(G37*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C37+D37+(E37*'03 Mind Knobs'!$B$17)+(F37*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F37))&gt;=MAX(0.15,0.35+(G37*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" t="n">
-        <x:f>--(MIN(1,C37+D37+(E37*'03 Mind Knobs'!$B$15)+(F37*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F37))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G37*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C37+D37+(E37*'03 Mind Knobs'!$B$17)+(F37*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F37))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G37*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K37" t="n">
@@ -46261,7 +47392,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L37" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A37,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B37-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B37))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M37" t="n">
@@ -46303,11 +47434,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I38" t="n">
-        <x:f>--(MIN(1,C38+D38+(E38*'03 Mind Knobs'!$B$15)+(F38*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F38))&gt;=MAX(0.15,0.35+(G38*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C38+D38+(E38*'03 Mind Knobs'!$B$17)+(F38*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F38))&gt;=MAX(0.15,0.35+(G38*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" t="n">
-        <x:f>--(MIN(1,C38+D38+(E38*'03 Mind Knobs'!$B$15)+(F38*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F38))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G38*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C38+D38+(E38*'03 Mind Knobs'!$B$17)+(F38*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F38))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G38*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K38" t="n">
@@ -46315,7 +47446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L38" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A38,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B38-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B38))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M38" t="n">
@@ -46357,11 +47488,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I39" t="n">
-        <x:f>--(MIN(1,C39+D39+(E39*'03 Mind Knobs'!$B$15)+(F39*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F39))&gt;=MAX(0.15,0.35+(G39*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C39+D39+(E39*'03 Mind Knobs'!$B$17)+(F39*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F39))&gt;=MAX(0.15,0.35+(G39*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" t="n">
-        <x:f>--(MIN(1,C39+D39+(E39*'03 Mind Knobs'!$B$15)+(F39*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F39))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G39*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C39+D39+(E39*'03 Mind Knobs'!$B$17)+(F39*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F39))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G39*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K39" t="n">
@@ -46369,7 +47500,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L39" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A39,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B39-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B39))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M39" t="n">
@@ -46411,11 +47542,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I40" t="n">
-        <x:f>--(MIN(1,C40+D40+(E40*'03 Mind Knobs'!$B$15)+(F40*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F40))&gt;=MAX(0.15,0.35+(G40*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C40+D40+(E40*'03 Mind Knobs'!$B$17)+(F40*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F40))&gt;=MAX(0.15,0.35+(G40*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J40" t="n">
-        <x:f>--(MIN(1,C40+D40+(E40*'03 Mind Knobs'!$B$15)+(F40*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F40))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G40*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C40+D40+(E40*'03 Mind Knobs'!$B$17)+(F40*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F40))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G40*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K40" t="n">
@@ -46423,7 +47554,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L40" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A40,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B40-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B40))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M40" t="n">
@@ -46465,11 +47596,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I41" t="n">
-        <x:f>--(MIN(1,C41+D41+(E41*'03 Mind Knobs'!$B$15)+(F41*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F41))&gt;=MAX(0.15,0.35+(G41*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C41+D41+(E41*'03 Mind Knobs'!$B$17)+(F41*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F41))&gt;=MAX(0.15,0.35+(G41*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" t="n">
-        <x:f>--(MIN(1,C41+D41+(E41*'03 Mind Knobs'!$B$15)+(F41*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F41))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G41*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C41+D41+(E41*'03 Mind Knobs'!$B$17)+(F41*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F41))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G41*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K41" t="n">
@@ -46477,7 +47608,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L41" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A41,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B41-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B41))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M41" t="n">
@@ -46519,11 +47650,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I42" t="n">
-        <x:f>--(MIN(1,C42+D42+(E42*'03 Mind Knobs'!$B$15)+(F42*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F42))&gt;=MAX(0.15,0.35+(G42*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C42+D42+(E42*'03 Mind Knobs'!$B$17)+(F42*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F42))&gt;=MAX(0.15,0.35+(G42*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J42" t="n">
-        <x:f>--(MIN(1,C42+D42+(E42*'03 Mind Knobs'!$B$15)+(F42*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F42))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G42*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C42+D42+(E42*'03 Mind Knobs'!$B$17)+(F42*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F42))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G42*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K42" t="n">
@@ -46531,7 +47662,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L42" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A42,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B42-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B42))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M42" t="n">
@@ -46573,11 +47704,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I43" t="n">
-        <x:f>--(MIN(1,C43+D43+(E43*'03 Mind Knobs'!$B$15)+(F43*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F43))&gt;=MAX(0.15,0.35+(G43*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C43+D43+(E43*'03 Mind Knobs'!$B$17)+(F43*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F43))&gt;=MAX(0.15,0.35+(G43*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" t="n">
-        <x:f>--(MIN(1,C43+D43+(E43*'03 Mind Knobs'!$B$15)+(F43*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F43))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G43*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C43+D43+(E43*'03 Mind Knobs'!$B$17)+(F43*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F43))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G43*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K43" t="n">
@@ -46585,7 +47716,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L43" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A43,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B43-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B43))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M43" t="n">
@@ -46627,11 +47758,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I44" t="n">
-        <x:f>--(MIN(1,C44+D44+(E44*'03 Mind Knobs'!$B$15)+(F44*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F44))&gt;=MAX(0.15,0.35+(G44*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C44+D44+(E44*'03 Mind Knobs'!$B$17)+(F44*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F44))&gt;=MAX(0.15,0.35+(G44*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J44" t="n">
-        <x:f>--(MIN(1,C44+D44+(E44*'03 Mind Knobs'!$B$15)+(F44*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F44))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G44*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C44+D44+(E44*'03 Mind Knobs'!$B$17)+(F44*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F44))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G44*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K44" t="n">
@@ -46639,7 +47770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L44" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A44,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B44-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B44))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M44" t="n">
@@ -46681,11 +47812,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I45" t="n">
-        <x:f>--(MIN(1,C45+D45+(E45*'03 Mind Knobs'!$B$15)+(F45*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F45))&gt;=MAX(0.15,0.35+(G45*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C45+D45+(E45*'03 Mind Knobs'!$B$17)+(F45*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F45))&gt;=MAX(0.15,0.35+(G45*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J45" t="n">
-        <x:f>--(MIN(1,C45+D45+(E45*'03 Mind Knobs'!$B$15)+(F45*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F45))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G45*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C45+D45+(E45*'03 Mind Knobs'!$B$17)+(F45*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F45))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G45*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K45" t="n">
@@ -46693,7 +47824,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L45" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A45,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B45-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B45))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M45" t="n">
@@ -46735,11 +47866,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I46" t="n">
-        <x:f>--(MIN(1,C46+D46+(E46*'03 Mind Knobs'!$B$15)+(F46*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F46))&gt;=MAX(0.15,0.35+(G46*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C46+D46+(E46*'03 Mind Knobs'!$B$17)+(F46*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F46))&gt;=MAX(0.15,0.35+(G46*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J46" t="n">
-        <x:f>--(MIN(1,C46+D46+(E46*'03 Mind Knobs'!$B$15)+(F46*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F46))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G46*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C46+D46+(E46*'03 Mind Knobs'!$B$17)+(F46*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F46))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G46*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K46" t="n">
@@ -46747,7 +47878,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L46" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A46,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B46-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B46))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M46" t="n">
@@ -46789,11 +47920,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I47" t="n">
-        <x:f>--(MIN(1,C47+D47+(E47*'03 Mind Knobs'!$B$15)+(F47*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F47))&gt;=MAX(0.15,0.35+(G47*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C47+D47+(E47*'03 Mind Knobs'!$B$17)+(F47*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F47))&gt;=MAX(0.15,0.35+(G47*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J47" t="n">
-        <x:f>--(MIN(1,C47+D47+(E47*'03 Mind Knobs'!$B$15)+(F47*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F47))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G47*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C47+D47+(E47*'03 Mind Knobs'!$B$17)+(F47*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F47))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G47*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K47" t="n">
@@ -46801,7 +47932,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L47" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A47,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B47-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B47))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M47" t="n">
@@ -46843,11 +47974,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I48" t="n">
-        <x:f>--(MIN(1,C48+D48+(E48*'03 Mind Knobs'!$B$15)+(F48*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F48))&gt;=MAX(0.15,0.35+(G48*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C48+D48+(E48*'03 Mind Knobs'!$B$17)+(F48*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F48))&gt;=MAX(0.15,0.35+(G48*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" t="n">
-        <x:f>--(MIN(1,C48+D48+(E48*'03 Mind Knobs'!$B$15)+(F48*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F48))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G48*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C48+D48+(E48*'03 Mind Knobs'!$B$17)+(F48*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F48))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G48*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K48" t="n">
@@ -46855,7 +47986,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L48" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A48,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B48-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B48))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M48" t="n">
@@ -46897,11 +48028,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I49" t="n">
-        <x:f>--(MIN(1,C49+D49+(E49*'03 Mind Knobs'!$B$15)+(F49*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F49))&gt;=MAX(0.15,0.35+(G49*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C49+D49+(E49*'03 Mind Knobs'!$B$17)+(F49*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F49))&gt;=MAX(0.15,0.35+(G49*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" t="n">
-        <x:f>--(MIN(1,C49+D49+(E49*'03 Mind Knobs'!$B$15)+(F49*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F49))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G49*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C49+D49+(E49*'03 Mind Knobs'!$B$17)+(F49*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F49))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G49*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K49" t="n">
@@ -46909,7 +48040,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L49" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A49,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B49-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B49))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M49" t="n">
@@ -46951,11 +48082,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I50" t="n">
-        <x:f>--(MIN(1,C50+D50+(E50*'03 Mind Knobs'!$B$15)+(F50*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F50))&gt;=MAX(0.15,0.35+(G50*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C50+D50+(E50*'03 Mind Knobs'!$B$17)+(F50*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F50))&gt;=MAX(0.15,0.35+(G50*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="n">
-        <x:f>--(MIN(1,C50+D50+(E50*'03 Mind Knobs'!$B$15)+(F50*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F50))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G50*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C50+D50+(E50*'03 Mind Knobs'!$B$17)+(F50*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F50))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G50*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K50" t="n">
@@ -46963,7 +48094,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L50" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A50,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B50-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B50))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M50" t="n">
@@ -47005,11 +48136,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" t="n">
-        <x:f>--(MIN(1,C51+D51+(E51*'03 Mind Knobs'!$B$15)+(F51*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F51))&gt;=MAX(0.15,0.35+(G51*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C51+D51+(E51*'03 Mind Knobs'!$B$17)+(F51*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F51))&gt;=MAX(0.15,0.35+(G51*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J51" t="n">
-        <x:f>--(MIN(1,C51+D51+(E51*'03 Mind Knobs'!$B$15)+(F51*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F51))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G51*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C51+D51+(E51*'03 Mind Knobs'!$B$17)+(F51*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F51))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G51*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K51" t="n">
@@ -47017,7 +48148,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L51" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A51,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B51-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B51))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M51" t="n">
@@ -47059,11 +48190,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I52" t="n">
-        <x:f>--(MIN(1,C52+D52+(E52*'03 Mind Knobs'!$B$15)+(F52*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F52))&gt;=MAX(0.15,0.35+(G52*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C52+D52+(E52*'03 Mind Knobs'!$B$17)+(F52*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F52))&gt;=MAX(0.15,0.35+(G52*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="n">
-        <x:f>--(MIN(1,C52+D52+(E52*'03 Mind Knobs'!$B$15)+(F52*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F52))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G52*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C52+D52+(E52*'03 Mind Knobs'!$B$17)+(F52*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F52))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G52*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K52" t="n">
@@ -47071,7 +48202,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L52" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A52,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B52-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B52))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M52" t="n">
@@ -47113,11 +48244,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I53" t="n">
-        <x:f>--(MIN(1,C53+D53+(E53*'03 Mind Knobs'!$B$15)+(F53*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F53))&gt;=MAX(0.15,0.35+(G53*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C53+D53+(E53*'03 Mind Knobs'!$B$17)+(F53*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F53))&gt;=MAX(0.15,0.35+(G53*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J53" t="n">
-        <x:f>--(MIN(1,C53+D53+(E53*'03 Mind Knobs'!$B$15)+(F53*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F53))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G53*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C53+D53+(E53*'03 Mind Knobs'!$B$17)+(F53*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F53))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G53*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K53" t="n">
@@ -47125,7 +48256,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L53" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A53,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B53-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B53))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M53" t="n">
@@ -47167,11 +48298,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I54" t="n">
-        <x:f>--(MIN(1,C54+D54+(E54*'03 Mind Knobs'!$B$15)+(F54*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F54))&gt;=MAX(0.15,0.35+(G54*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C54+D54+(E54*'03 Mind Knobs'!$B$17)+(F54*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F54))&gt;=MAX(0.15,0.35+(G54*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J54" t="n">
-        <x:f>--(MIN(1,C54+D54+(E54*'03 Mind Knobs'!$B$15)+(F54*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F54))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G54*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C54+D54+(E54*'03 Mind Knobs'!$B$17)+(F54*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F54))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G54*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K54" t="n">
@@ -47179,7 +48310,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L54" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A54,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B54-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B54))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M54" t="n">
@@ -47221,11 +48352,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I55" t="n">
-        <x:f>--(MIN(1,C55+D55+(E55*'03 Mind Knobs'!$B$15)+(F55*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F55))&gt;=MAX(0.15,0.35+(G55*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C55+D55+(E55*'03 Mind Knobs'!$B$17)+(F55*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F55))&gt;=MAX(0.15,0.35+(G55*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J55" t="n">
-        <x:f>--(MIN(1,C55+D55+(E55*'03 Mind Knobs'!$B$15)+(F55*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F55))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G55*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C55+D55+(E55*'03 Mind Knobs'!$B$17)+(F55*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F55))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G55*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K55" t="n">
@@ -47233,7 +48364,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L55" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A55,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B55-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B55))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M55" t="n">
@@ -47275,11 +48406,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I56" t="n">
-        <x:f>--(MIN(1,C56+D56+(E56*'03 Mind Knobs'!$B$15)+(F56*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F56))&gt;=MAX(0.15,0.35+(G56*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C56+D56+(E56*'03 Mind Knobs'!$B$17)+(F56*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F56))&gt;=MAX(0.15,0.35+(G56*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J56" t="n">
-        <x:f>--(MIN(1,C56+D56+(E56*'03 Mind Knobs'!$B$15)+(F56*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F56))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G56*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C56+D56+(E56*'03 Mind Knobs'!$B$17)+(F56*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F56))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G56*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K56" t="n">
@@ -47287,7 +48418,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L56" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A56,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B56-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B56))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M56" t="n">
@@ -47329,11 +48460,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I57" t="n">
-        <x:f>--(MIN(1,C57+D57+(E57*'03 Mind Knobs'!$B$15)+(F57*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F57))&gt;=MAX(0.15,0.35+(G57*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C57+D57+(E57*'03 Mind Knobs'!$B$17)+(F57*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F57))&gt;=MAX(0.15,0.35+(G57*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J57" t="n">
-        <x:f>--(MIN(1,C57+D57+(E57*'03 Mind Knobs'!$B$15)+(F57*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F57))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G57*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C57+D57+(E57*'03 Mind Knobs'!$B$17)+(F57*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F57))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G57*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K57" t="n">
@@ -47341,7 +48472,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L57" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A57,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B57-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B57))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M57" t="n">
@@ -47383,11 +48514,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I58" t="n">
-        <x:f>--(MIN(1,C58+D58+(E58*'03 Mind Knobs'!$B$15)+(F58*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F58))&gt;=MAX(0.15,0.35+(G58*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C58+D58+(E58*'03 Mind Knobs'!$B$17)+(F58*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F58))&gt;=MAX(0.15,0.35+(G58*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J58" t="n">
-        <x:f>--(MIN(1,C58+D58+(E58*'03 Mind Knobs'!$B$15)+(F58*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F58))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G58*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C58+D58+(E58*'03 Mind Knobs'!$B$17)+(F58*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F58))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G58*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K58" t="n">
@@ -47395,7 +48526,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L58" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A58,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B58-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B58))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M58" t="n">
@@ -47437,11 +48568,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I59" t="n">
-        <x:f>--(MIN(1,C59+D59+(E59*'03 Mind Knobs'!$B$15)+(F59*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F59))&gt;=MAX(0.15,0.35+(G59*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C59+D59+(E59*'03 Mind Knobs'!$B$17)+(F59*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F59))&gt;=MAX(0.15,0.35+(G59*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J59" t="n">
-        <x:f>--(MIN(1,C59+D59+(E59*'03 Mind Knobs'!$B$15)+(F59*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F59))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G59*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C59+D59+(E59*'03 Mind Knobs'!$B$17)+(F59*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F59))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G59*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K59" t="n">
@@ -47449,7 +48580,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L59" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A59,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B59-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B59))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M59" t="n">
@@ -47491,11 +48622,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I60" t="n">
-        <x:f>--(MIN(1,C60+D60+(E60*'03 Mind Knobs'!$B$15)+(F60*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F60))&gt;=MAX(0.15,0.35+(G60*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C60+D60+(E60*'03 Mind Knobs'!$B$17)+(F60*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F60))&gt;=MAX(0.15,0.35+(G60*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" t="n">
-        <x:f>--(MIN(1,C60+D60+(E60*'03 Mind Knobs'!$B$15)+(F60*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F60))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G60*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C60+D60+(E60*'03 Mind Knobs'!$B$17)+(F60*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F60))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G60*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K60" t="n">
@@ -47503,7 +48634,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L60" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A60,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B60-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B60))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M60" t="n">
@@ -47545,11 +48676,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I61" t="n">
-        <x:f>--(MIN(1,C61+D61+(E61*'03 Mind Knobs'!$B$15)+(F61*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F61))&gt;=MAX(0.15,0.35+(G61*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C61+D61+(E61*'03 Mind Knobs'!$B$17)+(F61*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F61))&gt;=MAX(0.15,0.35+(G61*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J61" t="n">
-        <x:f>--(MIN(1,C61+D61+(E61*'03 Mind Knobs'!$B$15)+(F61*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F61))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G61*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C61+D61+(E61*'03 Mind Knobs'!$B$17)+(F61*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F61))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G61*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K61" t="n">
@@ -47557,7 +48688,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L61" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A61,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B61-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B61))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M61" t="n">
@@ -47599,11 +48730,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I62" t="n">
-        <x:f>--(MIN(1,C62+D62+(E62*'03 Mind Knobs'!$B$15)+(F62*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F62))&gt;=MAX(0.15,0.35+(G62*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C62+D62+(E62*'03 Mind Knobs'!$B$17)+(F62*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F62))&gt;=MAX(0.15,0.35+(G62*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" t="n">
-        <x:f>--(MIN(1,C62+D62+(E62*'03 Mind Knobs'!$B$15)+(F62*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F62))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G62*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C62+D62+(E62*'03 Mind Knobs'!$B$17)+(F62*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F62))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G62*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K62" t="n">
@@ -47611,7 +48742,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L62" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A62,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B62-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B62))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M62" t="n">
@@ -47653,11 +48784,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I63" t="n">
-        <x:f>--(MIN(1,C63+D63+(E63*'03 Mind Knobs'!$B$15)+(F63*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F63))&gt;=MAX(0.15,0.35+(G63*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C63+D63+(E63*'03 Mind Knobs'!$B$17)+(F63*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F63))&gt;=MAX(0.15,0.35+(G63*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J63" t="n">
-        <x:f>--(MIN(1,C63+D63+(E63*'03 Mind Knobs'!$B$15)+(F63*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F63))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G63*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C63+D63+(E63*'03 Mind Knobs'!$B$17)+(F63*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F63))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G63*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K63" t="n">
@@ -47665,7 +48796,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L63" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A63,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B63-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B63))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M63" t="n">
@@ -47707,11 +48838,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I64" t="n">
-        <x:f>--(MIN(1,C64+D64+(E64*'03 Mind Knobs'!$B$15)+(F64*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F64))&gt;=MAX(0.15,0.35+(G64*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C64+D64+(E64*'03 Mind Knobs'!$B$17)+(F64*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F64))&gt;=MAX(0.15,0.35+(G64*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" t="n">
-        <x:f>--(MIN(1,C64+D64+(E64*'03 Mind Knobs'!$B$15)+(F64*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F64))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G64*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C64+D64+(E64*'03 Mind Knobs'!$B$17)+(F64*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F64))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G64*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K64" t="n">
@@ -47719,7 +48850,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L64" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A64,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B64-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B64))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M64" t="n">
@@ -47761,11 +48892,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I65" t="n">
-        <x:f>--(MIN(1,C65+D65+(E65*'03 Mind Knobs'!$B$15)+(F65*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F65))&gt;=MAX(0.15,0.35+(G65*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C65+D65+(E65*'03 Mind Knobs'!$B$17)+(F65*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F65))&gt;=MAX(0.15,0.35+(G65*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J65" t="n">
-        <x:f>--(MIN(1,C65+D65+(E65*'03 Mind Knobs'!$B$15)+(F65*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F65))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G65*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C65+D65+(E65*'03 Mind Knobs'!$B$17)+(F65*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F65))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G65*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K65" t="n">
@@ -47773,7 +48904,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L65" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A65,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B65-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B65))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M65" t="n">
@@ -47815,11 +48946,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I66" t="n">
-        <x:f>--(MIN(1,C66+D66+(E66*'03 Mind Knobs'!$B$15)+(F66*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F66))&gt;=MAX(0.15,0.35+(G66*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C66+D66+(E66*'03 Mind Knobs'!$B$17)+(F66*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F66))&gt;=MAX(0.15,0.35+(G66*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" t="n">
-        <x:f>--(MIN(1,C66+D66+(E66*'03 Mind Knobs'!$B$15)+(F66*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F66))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G66*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C66+D66+(E66*'03 Mind Knobs'!$B$17)+(F66*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F66))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G66*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K66" t="n">
@@ -47827,7 +48958,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L66" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A66,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B66-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B66))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M66" t="n">
@@ -47869,11 +49000,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I67" t="n">
-        <x:f>--(MIN(1,C67+D67+(E67*'03 Mind Knobs'!$B$15)+(F67*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F67))&gt;=MAX(0.15,0.35+(G67*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C67+D67+(E67*'03 Mind Knobs'!$B$17)+(F67*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F67))&gt;=MAX(0.15,0.35+(G67*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J67" t="n">
-        <x:f>--(MIN(1,C67+D67+(E67*'03 Mind Knobs'!$B$15)+(F67*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F67))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G67*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C67+D67+(E67*'03 Mind Knobs'!$B$17)+(F67*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F67))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G67*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K67" t="n">
@@ -47881,7 +49012,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L67" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A67,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B67-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B67))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M67" t="n">
@@ -47923,11 +49054,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I68" t="n">
-        <x:f>--(MIN(1,C68+D68+(E68*'03 Mind Knobs'!$B$15)+(F68*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F68))&gt;=MAX(0.15,0.35+(G68*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C68+D68+(E68*'03 Mind Knobs'!$B$17)+(F68*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F68))&gt;=MAX(0.15,0.35+(G68*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" t="n">
-        <x:f>--(MIN(1,C68+D68+(E68*'03 Mind Knobs'!$B$15)+(F68*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F68))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G68*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C68+D68+(E68*'03 Mind Knobs'!$B$17)+(F68*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F68))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G68*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K68" t="n">
@@ -47935,7 +49066,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L68" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A68,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B68-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B68))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M68" t="n">
@@ -47977,11 +49108,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I69" t="n">
-        <x:f>--(MIN(1,C69+D69+(E69*'03 Mind Knobs'!$B$15)+(F69*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F69))&gt;=MAX(0.15,0.35+(G69*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C69+D69+(E69*'03 Mind Knobs'!$B$17)+(F69*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F69))&gt;=MAX(0.15,0.35+(G69*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" t="n">
-        <x:f>--(MIN(1,C69+D69+(E69*'03 Mind Knobs'!$B$15)+(F69*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F69))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G69*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C69+D69+(E69*'03 Mind Knobs'!$B$17)+(F69*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F69))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G69*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K69" t="n">
@@ -47989,7 +49120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L69" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A69,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B69-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B69))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M69" t="n">
@@ -48031,11 +49162,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I70" t="n">
-        <x:f>--(MIN(1,C70+D70+(E70*'03 Mind Knobs'!$B$15)+(F70*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F70))&gt;=MAX(0.15,0.35+(G70*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C70+D70+(E70*'03 Mind Knobs'!$B$17)+(F70*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F70))&gt;=MAX(0.15,0.35+(G70*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" t="n">
-        <x:f>--(MIN(1,C70+D70+(E70*'03 Mind Knobs'!$B$15)+(F70*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F70))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G70*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C70+D70+(E70*'03 Mind Knobs'!$B$17)+(F70*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F70))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G70*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K70" t="n">
@@ -48043,7 +49174,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L70" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A70,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B70-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B70))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M70" t="n">
@@ -48085,11 +49216,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I71" t="n">
-        <x:f>--(MIN(1,C71+D71+(E71*'03 Mind Knobs'!$B$15)+(F71*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F71))&gt;=MAX(0.15,0.35+(G71*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C71+D71+(E71*'03 Mind Knobs'!$B$17)+(F71*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F71))&gt;=MAX(0.15,0.35+(G71*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J71" t="n">
-        <x:f>--(MIN(1,C71+D71+(E71*'03 Mind Knobs'!$B$15)+(F71*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F71))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G71*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C71+D71+(E71*'03 Mind Knobs'!$B$17)+(F71*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F71))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G71*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K71" t="n">
@@ -48097,7 +49228,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L71" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A71,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B71-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B71))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M71" t="n">
@@ -48139,11 +49270,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I72" t="n">
-        <x:f>--(MIN(1,C72+D72+(E72*'03 Mind Knobs'!$B$15)+(F72*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F72))&gt;=MAX(0.15,0.35+(G72*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C72+D72+(E72*'03 Mind Knobs'!$B$17)+(F72*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F72))&gt;=MAX(0.15,0.35+(G72*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J72" t="n">
-        <x:f>--(MIN(1,C72+D72+(E72*'03 Mind Knobs'!$B$15)+(F72*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F72))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G72*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C72+D72+(E72*'03 Mind Knobs'!$B$17)+(F72*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F72))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G72*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K72" t="n">
@@ -48151,7 +49282,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L72" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A72,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B72-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B72))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M72" t="n">
@@ -48193,11 +49324,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I73" t="n">
-        <x:f>--(MIN(1,C73+D73+(E73*'03 Mind Knobs'!$B$15)+(F73*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F73))&gt;=MAX(0.15,0.35+(G73*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C73+D73+(E73*'03 Mind Knobs'!$B$17)+(F73*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F73))&gt;=MAX(0.15,0.35+(G73*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J73" t="n">
-        <x:f>--(MIN(1,C73+D73+(E73*'03 Mind Knobs'!$B$15)+(F73*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F73))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G73*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C73+D73+(E73*'03 Mind Knobs'!$B$17)+(F73*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F73))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G73*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K73" t="n">
@@ -48205,7 +49336,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L73" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A73,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B73-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B73))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M73" t="n">
@@ -48247,11 +49378,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I74" t="n">
-        <x:f>--(MIN(1,C74+D74+(E74*'03 Mind Knobs'!$B$15)+(F74*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F74))&gt;=MAX(0.15,0.35+(G74*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C74+D74+(E74*'03 Mind Knobs'!$B$17)+(F74*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F74))&gt;=MAX(0.15,0.35+(G74*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J74" t="n">
-        <x:f>--(MIN(1,C74+D74+(E74*'03 Mind Knobs'!$B$15)+(F74*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F74))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G74*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C74+D74+(E74*'03 Mind Knobs'!$B$17)+(F74*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F74))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G74*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K74" t="n">
@@ -48259,7 +49390,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L74" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A74,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B74-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B74))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M74" t="n">
@@ -48301,11 +49432,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I75" t="n">
-        <x:f>--(MIN(1,C75+D75+(E75*'03 Mind Knobs'!$B$15)+(F75*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F75))&gt;=MAX(0.15,0.35+(G75*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C75+D75+(E75*'03 Mind Knobs'!$B$17)+(F75*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F75))&gt;=MAX(0.15,0.35+(G75*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" t="n">
-        <x:f>--(MIN(1,C75+D75+(E75*'03 Mind Knobs'!$B$15)+(F75*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F75))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G75*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C75+D75+(E75*'03 Mind Knobs'!$B$17)+(F75*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F75))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G75*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K75" t="n">
@@ -48313,7 +49444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L75" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A75,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B75-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B75))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M75" t="n">
@@ -48355,11 +49486,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I76" t="n">
-        <x:f>--(MIN(1,C76+D76+(E76*'03 Mind Knobs'!$B$15)+(F76*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F76))&gt;=MAX(0.15,0.35+(G76*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C76+D76+(E76*'03 Mind Knobs'!$B$17)+(F76*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F76))&gt;=MAX(0.15,0.35+(G76*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J76" t="n">
-        <x:f>--(MIN(1,C76+D76+(E76*'03 Mind Knobs'!$B$15)+(F76*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F76))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G76*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C76+D76+(E76*'03 Mind Knobs'!$B$17)+(F76*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F76))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G76*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K76" t="n">
@@ -48367,7 +49498,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L76" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A76,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B76-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B76))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M76" t="n">
@@ -48409,11 +49540,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I77" t="n">
-        <x:f>--(MIN(1,C77+D77+(E77*'03 Mind Knobs'!$B$15)+(F77*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F77))&gt;=MAX(0.15,0.35+(G77*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C77+D77+(E77*'03 Mind Knobs'!$B$17)+(F77*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F77))&gt;=MAX(0.15,0.35+(G77*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J77" t="n">
-        <x:f>--(MIN(1,C77+D77+(E77*'03 Mind Knobs'!$B$15)+(F77*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F77))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G77*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C77+D77+(E77*'03 Mind Knobs'!$B$17)+(F77*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F77))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G77*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K77" t="n">
@@ -48421,7 +49552,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L77" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A77,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B77-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B77))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M77" t="n">
@@ -48463,11 +49594,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I78" t="n">
-        <x:f>--(MIN(1,C78+D78+(E78*'03 Mind Knobs'!$B$15)+(F78*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F78))&gt;=MAX(0.15,0.35+(G78*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C78+D78+(E78*'03 Mind Knobs'!$B$17)+(F78*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F78))&gt;=MAX(0.15,0.35+(G78*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J78" t="n">
-        <x:f>--(MIN(1,C78+D78+(E78*'03 Mind Knobs'!$B$15)+(F78*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F78))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G78*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C78+D78+(E78*'03 Mind Knobs'!$B$17)+(F78*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F78))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G78*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K78" t="n">
@@ -48475,7 +49606,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L78" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A78,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B78-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B78))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M78" t="n">
@@ -48517,11 +49648,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I79" t="n">
-        <x:f>--(MIN(1,C79+D79+(E79*'03 Mind Knobs'!$B$15)+(F79*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F79))&gt;=MAX(0.15,0.35+(G79*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C79+D79+(E79*'03 Mind Knobs'!$B$17)+(F79*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F79))&gt;=MAX(0.15,0.35+(G79*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" t="n">
-        <x:f>--(MIN(1,C79+D79+(E79*'03 Mind Knobs'!$B$15)+(F79*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F79))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G79*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C79+D79+(E79*'03 Mind Knobs'!$B$17)+(F79*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F79))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G79*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K79" t="n">
@@ -48529,7 +49660,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L79" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A79,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B79-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B79))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M79" t="n">
@@ -48571,11 +49702,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I80" t="n">
-        <x:f>--(MIN(1,C80+D80+(E80*'03 Mind Knobs'!$B$15)+(F80*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F80))&gt;=MAX(0.15,0.35+(G80*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C80+D80+(E80*'03 Mind Knobs'!$B$17)+(F80*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F80))&gt;=MAX(0.15,0.35+(G80*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" t="n">
-        <x:f>--(MIN(1,C80+D80+(E80*'03 Mind Knobs'!$B$15)+(F80*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F80))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G80*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C80+D80+(E80*'03 Mind Knobs'!$B$17)+(F80*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F80))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G80*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K80" t="n">
@@ -48583,7 +49714,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L80" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A80,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B80-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B80))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M80" t="n">
@@ -48625,11 +49756,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I81" t="n">
-        <x:f>--(MIN(1,C81+D81+(E81*'03 Mind Knobs'!$B$15)+(F81*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F81))&gt;=MAX(0.15,0.35+(G81*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C81+D81+(E81*'03 Mind Knobs'!$B$17)+(F81*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F81))&gt;=MAX(0.15,0.35+(G81*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" t="n">
-        <x:f>--(MIN(1,C81+D81+(E81*'03 Mind Knobs'!$B$15)+(F81*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F81))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G81*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C81+D81+(E81*'03 Mind Knobs'!$B$17)+(F81*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F81))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G81*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K81" t="n">
@@ -48637,7 +49768,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L81" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A81,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B81-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B81))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M81" t="n">
@@ -48679,11 +49810,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I82" t="n">
-        <x:f>--(MIN(1,C82+D82+(E82*'03 Mind Knobs'!$B$15)+(F82*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F82))&gt;=MAX(0.15,0.35+(G82*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C82+D82+(E82*'03 Mind Knobs'!$B$17)+(F82*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F82))&gt;=MAX(0.15,0.35+(G82*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J82" t="n">
-        <x:f>--(MIN(1,C82+D82+(E82*'03 Mind Knobs'!$B$15)+(F82*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F82))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G82*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C82+D82+(E82*'03 Mind Knobs'!$B$17)+(F82*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F82))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G82*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K82" t="n">
@@ -48691,7 +49822,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L82" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A82,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B82-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B82))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M82" t="n">
@@ -48733,11 +49864,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I83" t="n">
-        <x:f>--(MIN(1,C83+D83+(E83*'03 Mind Knobs'!$B$15)+(F83*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F83))&gt;=MAX(0.15,0.35+(G83*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C83+D83+(E83*'03 Mind Knobs'!$B$17)+(F83*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F83))&gt;=MAX(0.15,0.35+(G83*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J83" t="n">
-        <x:f>--(MIN(1,C83+D83+(E83*'03 Mind Knobs'!$B$15)+(F83*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F83))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G83*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C83+D83+(E83*'03 Mind Knobs'!$B$17)+(F83*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F83))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G83*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K83" t="n">
@@ -48745,7 +49876,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L83" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A83,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B83-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B83))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M83" t="n">
@@ -48787,11 +49918,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I84" t="n">
-        <x:f>--(MIN(1,C84+D84+(E84*'03 Mind Knobs'!$B$15)+(F84*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F84))&gt;=MAX(0.15,0.35+(G84*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C84+D84+(E84*'03 Mind Knobs'!$B$17)+(F84*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F84))&gt;=MAX(0.15,0.35+(G84*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J84" t="n">
-        <x:f>--(MIN(1,C84+D84+(E84*'03 Mind Knobs'!$B$15)+(F84*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F84))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G84*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C84+D84+(E84*'03 Mind Knobs'!$B$17)+(F84*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F84))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G84*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K84" t="n">
@@ -48799,7 +49930,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L84" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A84,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B84-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B84))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M84" t="n">
@@ -48841,11 +49972,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I85" t="n">
-        <x:f>--(MIN(1,C85+D85+(E85*'03 Mind Knobs'!$B$15)+(F85*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F85))&gt;=MAX(0.15,0.35+(G85*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C85+D85+(E85*'03 Mind Knobs'!$B$17)+(F85*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F85))&gt;=MAX(0.15,0.35+(G85*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J85" t="n">
-        <x:f>--(MIN(1,C85+D85+(E85*'03 Mind Knobs'!$B$15)+(F85*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F85))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G85*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C85+D85+(E85*'03 Mind Knobs'!$B$17)+(F85*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F85))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G85*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K85" t="n">
@@ -48853,7 +49984,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L85" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A85,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B85-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B85))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M85" t="n">
@@ -48895,11 +50026,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I86" t="n">
-        <x:f>--(MIN(1,C86+D86+(E86*'03 Mind Knobs'!$B$15)+(F86*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F86))&gt;=MAX(0.15,0.35+(G86*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C86+D86+(E86*'03 Mind Knobs'!$B$17)+(F86*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F86))&gt;=MAX(0.15,0.35+(G86*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J86" t="n">
-        <x:f>--(MIN(1,C86+D86+(E86*'03 Mind Knobs'!$B$15)+(F86*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F86))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G86*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C86+D86+(E86*'03 Mind Knobs'!$B$17)+(F86*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F86))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G86*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K86" t="n">
@@ -48907,7 +50038,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L86" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A86,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B86-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B86))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M86" t="n">
@@ -48949,11 +50080,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I87" t="n">
-        <x:f>--(MIN(1,C87+D87+(E87*'03 Mind Knobs'!$B$15)+(F87*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F87))&gt;=MAX(0.15,0.35+(G87*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C87+D87+(E87*'03 Mind Knobs'!$B$17)+(F87*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F87))&gt;=MAX(0.15,0.35+(G87*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J87" t="n">
-        <x:f>--(MIN(1,C87+D87+(E87*'03 Mind Knobs'!$B$15)+(F87*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F87))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G87*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C87+D87+(E87*'03 Mind Knobs'!$B$17)+(F87*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F87))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G87*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K87" t="n">
@@ -48961,7 +50092,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L87" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A87,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B87-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B87))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M87" t="n">
@@ -49003,11 +50134,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I88" t="n">
-        <x:f>--(MIN(1,C88+D88+(E88*'03 Mind Knobs'!$B$15)+(F88*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F88))&gt;=MAX(0.15,0.35+(G88*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C88+D88+(E88*'03 Mind Knobs'!$B$17)+(F88*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F88))&gt;=MAX(0.15,0.35+(G88*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J88" t="n">
-        <x:f>--(MIN(1,C88+D88+(E88*'03 Mind Knobs'!$B$15)+(F88*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F88))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G88*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C88+D88+(E88*'03 Mind Knobs'!$B$17)+(F88*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F88))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G88*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K88" t="n">
@@ -49015,7 +50146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L88" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A88,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B88-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B88))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M88" t="n">
@@ -49057,11 +50188,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I89" t="n">
-        <x:f>--(MIN(1,C89+D89+(E89*'03 Mind Knobs'!$B$15)+(F89*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F89))&gt;=MAX(0.15,0.35+(G89*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C89+D89+(E89*'03 Mind Knobs'!$B$17)+(F89*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F89))&gt;=MAX(0.15,0.35+(G89*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J89" t="n">
-        <x:f>--(MIN(1,C89+D89+(E89*'03 Mind Knobs'!$B$15)+(F89*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F89))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G89*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C89+D89+(E89*'03 Mind Knobs'!$B$17)+(F89*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F89))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G89*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K89" t="n">
@@ -49069,7 +50200,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L89" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A89,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B89-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B89))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M89" t="n">
@@ -49111,11 +50242,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I90" t="n">
-        <x:f>--(MIN(1,C90+D90+(E90*'03 Mind Knobs'!$B$15)+(F90*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F90))&gt;=MAX(0.15,0.35+(G90*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C90+D90+(E90*'03 Mind Knobs'!$B$17)+(F90*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F90))&gt;=MAX(0.15,0.35+(G90*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J90" t="n">
-        <x:f>--(MIN(1,C90+D90+(E90*'03 Mind Knobs'!$B$15)+(F90*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F90))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G90*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C90+D90+(E90*'03 Mind Knobs'!$B$17)+(F90*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F90))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G90*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K90" t="n">
@@ -49123,7 +50254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L90" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A90,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B90-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B90))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M90" t="n">
@@ -49165,11 +50296,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I91" t="n">
-        <x:f>--(MIN(1,C91+D91+(E91*'03 Mind Knobs'!$B$15)+(F91*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F91))&gt;=MAX(0.15,0.35+(G91*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C91+D91+(E91*'03 Mind Knobs'!$B$17)+(F91*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F91))&gt;=MAX(0.15,0.35+(G91*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J91" t="n">
-        <x:f>--(MIN(1,C91+D91+(E91*'03 Mind Knobs'!$B$15)+(F91*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F91))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G91*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C91+D91+(E91*'03 Mind Knobs'!$B$17)+(F91*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F91))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G91*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K91" t="n">
@@ -49177,7 +50308,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L91" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A91,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B91-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B91))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M91" t="n">
@@ -49219,11 +50350,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I92" t="n">
-        <x:f>--(MIN(1,C92+D92+(E92*'03 Mind Knobs'!$B$15)+(F92*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F92))&gt;=MAX(0.15,0.35+(G92*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C92+D92+(E92*'03 Mind Knobs'!$B$17)+(F92*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F92))&gt;=MAX(0.15,0.35+(G92*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J92" t="n">
-        <x:f>--(MIN(1,C92+D92+(E92*'03 Mind Knobs'!$B$15)+(F92*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F92))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G92*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C92+D92+(E92*'03 Mind Knobs'!$B$17)+(F92*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F92))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G92*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K92" t="n">
@@ -49231,7 +50362,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L92" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A92,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B92-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B92))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M92" t="n">
@@ -49273,11 +50404,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I93" t="n">
-        <x:f>--(MIN(1,C93+D93+(E93*'03 Mind Knobs'!$B$15)+(F93*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F93))&gt;=MAX(0.15,0.35+(G93*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C93+D93+(E93*'03 Mind Knobs'!$B$17)+(F93*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F93))&gt;=MAX(0.15,0.35+(G93*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J93" t="n">
-        <x:f>--(MIN(1,C93+D93+(E93*'03 Mind Knobs'!$B$15)+(F93*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F93))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G93*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C93+D93+(E93*'03 Mind Knobs'!$B$17)+(F93*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F93))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G93*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K93" t="n">
@@ -49285,7 +50416,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L93" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A93,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B93-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B93))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M93" t="n">
@@ -49327,11 +50458,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I94" t="n">
-        <x:f>--(MIN(1,C94+D94+(E94*'03 Mind Knobs'!$B$15)+(F94*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F94))&gt;=MAX(0.15,0.35+(G94*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C94+D94+(E94*'03 Mind Knobs'!$B$17)+(F94*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F94))&gt;=MAX(0.15,0.35+(G94*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J94" t="n">
-        <x:f>--(MIN(1,C94+D94+(E94*'03 Mind Knobs'!$B$15)+(F94*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F94))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G94*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C94+D94+(E94*'03 Mind Knobs'!$B$17)+(F94*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F94))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G94*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K94" t="n">
@@ -49339,7 +50470,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L94" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A94,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B94-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B94))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M94" t="n">
@@ -49381,11 +50512,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I95" t="n">
-        <x:f>--(MIN(1,C95+D95+(E95*'03 Mind Knobs'!$B$15)+(F95*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F95))&gt;=MAX(0.15,0.35+(G95*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C95+D95+(E95*'03 Mind Knobs'!$B$17)+(F95*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F95))&gt;=MAX(0.15,0.35+(G95*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J95" t="n">
-        <x:f>--(MIN(1,C95+D95+(E95*'03 Mind Knobs'!$B$15)+(F95*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F95))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G95*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C95+D95+(E95*'03 Mind Knobs'!$B$17)+(F95*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F95))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G95*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K95" t="n">
@@ -49393,7 +50524,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L95" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A95,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B95-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B95))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M95" t="n">
@@ -49435,11 +50566,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I96" t="n">
-        <x:f>--(MIN(1,C96+D96+(E96*'03 Mind Knobs'!$B$15)+(F96*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F96))&gt;=MAX(0.15,0.35+(G96*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C96+D96+(E96*'03 Mind Knobs'!$B$17)+(F96*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F96))&gt;=MAX(0.15,0.35+(G96*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J96" t="n">
-        <x:f>--(MIN(1,C96+D96+(E96*'03 Mind Knobs'!$B$15)+(F96*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F96))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G96*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C96+D96+(E96*'03 Mind Knobs'!$B$17)+(F96*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F96))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G96*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K96" t="n">
@@ -49447,7 +50578,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L96" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A96,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B96-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B96))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M96" t="n">
@@ -49489,11 +50620,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I97" t="n">
-        <x:f>--(MIN(1,C97+D97+(E97*'03 Mind Knobs'!$B$15)+(F97*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F97))&gt;=MAX(0.15,0.35+(G97*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C97+D97+(E97*'03 Mind Knobs'!$B$17)+(F97*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F97))&gt;=MAX(0.15,0.35+(G97*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J97" t="n">
-        <x:f>--(MIN(1,C97+D97+(E97*'03 Mind Knobs'!$B$15)+(F97*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F97))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G97*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C97+D97+(E97*'03 Mind Knobs'!$B$17)+(F97*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F97))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G97*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K97" t="n">
@@ -49501,7 +50632,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L97" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A97,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B97-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B97))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M97" t="n">
@@ -49543,11 +50674,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I98" t="n">
-        <x:f>--(MIN(1,C98+D98+(E98*'03 Mind Knobs'!$B$15)+(F98*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F98))&gt;=MAX(0.15,0.35+(G98*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C98+D98+(E98*'03 Mind Knobs'!$B$17)+(F98*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F98))&gt;=MAX(0.15,0.35+(G98*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J98" t="n">
-        <x:f>--(MIN(1,C98+D98+(E98*'03 Mind Knobs'!$B$15)+(F98*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F98))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G98*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C98+D98+(E98*'03 Mind Knobs'!$B$17)+(F98*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F98))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G98*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K98" t="n">
@@ -49555,7 +50686,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L98" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A98,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B98-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B98))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M98" t="n">
@@ -49597,11 +50728,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I99" t="n">
-        <x:f>--(MIN(1,C99+D99+(E99*'03 Mind Knobs'!$B$15)+(F99*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F99))&gt;=MAX(0.15,0.35+(G99*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C99+D99+(E99*'03 Mind Knobs'!$B$17)+(F99*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F99))&gt;=MAX(0.15,0.35+(G99*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J99" t="n">
-        <x:f>--(MIN(1,C99+D99+(E99*'03 Mind Knobs'!$B$15)+(F99*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F99))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G99*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C99+D99+(E99*'03 Mind Knobs'!$B$17)+(F99*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F99))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G99*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K99" t="n">
@@ -49609,7 +50740,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L99" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A99,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B99-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B99))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M99" t="n">
@@ -49651,11 +50782,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I100" t="n">
-        <x:f>--(MIN(1,C100+D100+(E100*'03 Mind Knobs'!$B$15)+(F100*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F100))&gt;=MAX(0.15,0.35+(G100*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C100+D100+(E100*'03 Mind Knobs'!$B$17)+(F100*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F100))&gt;=MAX(0.15,0.35+(G100*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J100" t="n">
-        <x:f>--(MIN(1,C100+D100+(E100*'03 Mind Knobs'!$B$15)+(F100*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F100))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G100*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C100+D100+(E100*'03 Mind Knobs'!$B$17)+(F100*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F100))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G100*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K100" t="n">
@@ -49663,7 +50794,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L100" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A100,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B100-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B100))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M100" t="n">
@@ -49705,11 +50836,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I101" t="n">
-        <x:f>--(MIN(1,C101+D101+(E101*'03 Mind Knobs'!$B$15)+(F101*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F101))&gt;=MAX(0.15,0.35+(G101*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C101+D101+(E101*'03 Mind Knobs'!$B$17)+(F101*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F101))&gt;=MAX(0.15,0.35+(G101*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J101" t="n">
-        <x:f>--(MIN(1,C101+D101+(E101*'03 Mind Knobs'!$B$15)+(F101*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F101))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G101*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C101+D101+(E101*'03 Mind Knobs'!$B$17)+(F101*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F101))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G101*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K101" t="n">
@@ -49717,7 +50848,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L101" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A101,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B101-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B101))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M101" t="n">
@@ -49759,11 +50890,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I102" t="n">
-        <x:f>--(MIN(1,C102+D102+(E102*'03 Mind Knobs'!$B$15)+(F102*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F102))&gt;=MAX(0.15,0.35+(G102*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C102+D102+(E102*'03 Mind Knobs'!$B$17)+(F102*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F102))&gt;=MAX(0.15,0.35+(G102*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J102" t="n">
-        <x:f>--(MIN(1,C102+D102+(E102*'03 Mind Knobs'!$B$15)+(F102*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F102))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G102*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C102+D102+(E102*'03 Mind Knobs'!$B$17)+(F102*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F102))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G102*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K102" t="n">
@@ -49771,7 +50902,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L102" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A102,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B102-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B102))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M102" t="n">
@@ -49813,11 +50944,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I103" t="n">
-        <x:f>--(MIN(1,C103+D103+(E103*'03 Mind Knobs'!$B$15)+(F103*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F103))&gt;=MAX(0.15,0.35+(G103*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C103+D103+(E103*'03 Mind Knobs'!$B$17)+(F103*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F103))&gt;=MAX(0.15,0.35+(G103*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J103" t="n">
-        <x:f>--(MIN(1,C103+D103+(E103*'03 Mind Knobs'!$B$15)+(F103*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F103))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G103*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C103+D103+(E103*'03 Mind Knobs'!$B$17)+(F103*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F103))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G103*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K103" t="n">
@@ -49825,7 +50956,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L103" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A103,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B103-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B103))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M103" t="n">
@@ -49867,11 +50998,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I104" t="n">
-        <x:f>--(MIN(1,C104+D104+(E104*'03 Mind Knobs'!$B$15)+(F104*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F104))&gt;=MAX(0.15,0.35+(G104*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C104+D104+(E104*'03 Mind Knobs'!$B$17)+(F104*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F104))&gt;=MAX(0.15,0.35+(G104*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J104" t="n">
-        <x:f>--(MIN(1,C104+D104+(E104*'03 Mind Knobs'!$B$15)+(F104*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F104))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G104*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C104+D104+(E104*'03 Mind Knobs'!$B$17)+(F104*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F104))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G104*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K104" t="n">
@@ -49879,7 +51010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L104" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A104,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B104-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B104))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M104" t="n">
@@ -49921,11 +51052,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I105" t="n">
-        <x:f>--(MIN(1,C105+D105+(E105*'03 Mind Knobs'!$B$15)+(F105*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F105))&gt;=MAX(0.15,0.35+(G105*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C105+D105+(E105*'03 Mind Knobs'!$B$17)+(F105*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F105))&gt;=MAX(0.15,0.35+(G105*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J105" t="n">
-        <x:f>--(MIN(1,C105+D105+(E105*'03 Mind Knobs'!$B$15)+(F105*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F105))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G105*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C105+D105+(E105*'03 Mind Knobs'!$B$17)+(F105*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F105))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G105*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K105" t="n">
@@ -49933,7 +51064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L105" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A105,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B105-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B105))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M105" t="n">
@@ -49975,11 +51106,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I106" t="n">
-        <x:f>--(MIN(1,C106+D106+(E106*'03 Mind Knobs'!$B$15)+(F106*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F106))&gt;=MAX(0.15,0.35+(G106*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C106+D106+(E106*'03 Mind Knobs'!$B$17)+(F106*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F106))&gt;=MAX(0.15,0.35+(G106*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J106" t="n">
-        <x:f>--(MIN(1,C106+D106+(E106*'03 Mind Knobs'!$B$15)+(F106*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F106))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G106*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C106+D106+(E106*'03 Mind Knobs'!$B$17)+(F106*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F106))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G106*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K106" t="n">
@@ -49987,7 +51118,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L106" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A106,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B106-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B106))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M106" t="n">
@@ -50029,11 +51160,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I107" t="n">
-        <x:f>--(MIN(1,C107+D107+(E107*'03 Mind Knobs'!$B$15)+(F107*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F107))&gt;=MAX(0.15,0.35+(G107*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C107+D107+(E107*'03 Mind Knobs'!$B$17)+(F107*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F107))&gt;=MAX(0.15,0.35+(G107*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J107" t="n">
-        <x:f>--(MIN(1,C107+D107+(E107*'03 Mind Knobs'!$B$15)+(F107*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F107))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G107*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C107+D107+(E107*'03 Mind Knobs'!$B$17)+(F107*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F107))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G107*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K107" t="n">
@@ -50041,7 +51172,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L107" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A107,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B107-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B107))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M107" t="n">
@@ -50083,11 +51214,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I108" t="n">
-        <x:f>--(MIN(1,C108+D108+(E108*'03 Mind Knobs'!$B$15)+(F108*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F108))&gt;=MAX(0.15,0.35+(G108*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C108+D108+(E108*'03 Mind Knobs'!$B$17)+(F108*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F108))&gt;=MAX(0.15,0.35+(G108*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J108" t="n">
-        <x:f>--(MIN(1,C108+D108+(E108*'03 Mind Knobs'!$B$15)+(F108*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F108))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G108*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C108+D108+(E108*'03 Mind Knobs'!$B$17)+(F108*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F108))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G108*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K108" t="n">
@@ -50095,7 +51226,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L108" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A108,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B108-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B108))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M108" t="n">
@@ -50137,11 +51268,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I109" t="n">
-        <x:f>--(MIN(1,C109+D109+(E109*'03 Mind Knobs'!$B$15)+(F109*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F109))&gt;=MAX(0.15,0.35+(G109*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C109+D109+(E109*'03 Mind Knobs'!$B$17)+(F109*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F109))&gt;=MAX(0.15,0.35+(G109*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J109" t="n">
-        <x:f>--(MIN(1,C109+D109+(E109*'03 Mind Knobs'!$B$15)+(F109*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F109))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G109*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C109+D109+(E109*'03 Mind Knobs'!$B$17)+(F109*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F109))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G109*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K109" t="n">
@@ -50149,7 +51280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L109" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A109,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B109-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B109))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M109" t="n">
@@ -50191,11 +51322,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I110" t="n">
-        <x:f>--(MIN(1,C110+D110+(E110*'03 Mind Knobs'!$B$15)+(F110*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F110))&gt;=MAX(0.15,0.35+(G110*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C110+D110+(E110*'03 Mind Knobs'!$B$17)+(F110*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F110))&gt;=MAX(0.15,0.35+(G110*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J110" t="n">
-        <x:f>--(MIN(1,C110+D110+(E110*'03 Mind Knobs'!$B$15)+(F110*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F110))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G110*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C110+D110+(E110*'03 Mind Knobs'!$B$17)+(F110*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F110))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G110*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K110" t="n">
@@ -50203,7 +51334,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L110" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A110,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B110-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B110))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M110" t="n">
@@ -50245,11 +51376,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I111" t="n">
-        <x:f>--(MIN(1,C111+D111+(E111*'03 Mind Knobs'!$B$15)+(F111*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F111))&gt;=MAX(0.15,0.35+(G111*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C111+D111+(E111*'03 Mind Knobs'!$B$17)+(F111*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F111))&gt;=MAX(0.15,0.35+(G111*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J111" t="n">
-        <x:f>--(MIN(1,C111+D111+(E111*'03 Mind Knobs'!$B$15)+(F111*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F111))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G111*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C111+D111+(E111*'03 Mind Knobs'!$B$17)+(F111*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F111))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G111*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K111" t="n">
@@ -50257,7 +51388,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L111" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A111,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B111-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B111))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M111" t="n">
@@ -50299,11 +51430,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I112" t="n">
-        <x:f>--(MIN(1,C112+D112+(E112*'03 Mind Knobs'!$B$15)+(F112*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F112))&gt;=MAX(0.15,0.35+(G112*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C112+D112+(E112*'03 Mind Knobs'!$B$17)+(F112*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F112))&gt;=MAX(0.15,0.35+(G112*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J112" t="n">
-        <x:f>--(MIN(1,C112+D112+(E112*'03 Mind Knobs'!$B$15)+(F112*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F112))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G112*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C112+D112+(E112*'03 Mind Knobs'!$B$17)+(F112*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F112))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G112*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K112" t="n">
@@ -50311,7 +51442,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L112" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A112,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B112-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B112))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M112" t="n">
@@ -50353,11 +51484,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I113" t="n">
-        <x:f>--(MIN(1,C113+D113+(E113*'03 Mind Knobs'!$B$15)+(F113*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F113))&gt;=MAX(0.15,0.35+(G113*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C113+D113+(E113*'03 Mind Knobs'!$B$17)+(F113*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F113))&gt;=MAX(0.15,0.35+(G113*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J113" t="n">
-        <x:f>--(MIN(1,C113+D113+(E113*'03 Mind Knobs'!$B$15)+(F113*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F113))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G113*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C113+D113+(E113*'03 Mind Knobs'!$B$17)+(F113*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F113))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G113*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K113" t="n">
@@ -50365,7 +51496,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L113" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A113,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B113-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B113))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M113" t="n">
@@ -50407,11 +51538,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I114" t="n">
-        <x:f>--(MIN(1,C114+D114+(E114*'03 Mind Knobs'!$B$15)+(F114*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F114))&gt;=MAX(0.15,0.35+(G114*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C114+D114+(E114*'03 Mind Knobs'!$B$17)+(F114*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F114))&gt;=MAX(0.15,0.35+(G114*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J114" t="n">
-        <x:f>--(MIN(1,C114+D114+(E114*'03 Mind Knobs'!$B$15)+(F114*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F114))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G114*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C114+D114+(E114*'03 Mind Knobs'!$B$17)+(F114*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F114))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G114*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K114" t="n">
@@ -50419,7 +51550,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L114" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A114,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B114-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B114))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M114" t="n">
@@ -50461,11 +51592,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I115" t="n">
-        <x:f>--(MIN(1,C115+D115+(E115*'03 Mind Knobs'!$B$15)+(F115*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F115))&gt;=MAX(0.15,0.35+(G115*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C115+D115+(E115*'03 Mind Knobs'!$B$17)+(F115*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F115))&gt;=MAX(0.15,0.35+(G115*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J115" t="n">
-        <x:f>--(MIN(1,C115+D115+(E115*'03 Mind Knobs'!$B$15)+(F115*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F115))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G115*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C115+D115+(E115*'03 Mind Knobs'!$B$17)+(F115*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F115))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G115*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K115" t="n">
@@ -50473,7 +51604,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L115" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A115,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B115-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B115))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M115" t="n">
@@ -50515,11 +51646,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I116" t="n">
-        <x:f>--(MIN(1,C116+D116+(E116*'03 Mind Knobs'!$B$15)+(F116*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F116))&gt;=MAX(0.15,0.35+(G116*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C116+D116+(E116*'03 Mind Knobs'!$B$17)+(F116*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F116))&gt;=MAX(0.15,0.35+(G116*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J116" t="n">
-        <x:f>--(MIN(1,C116+D116+(E116*'03 Mind Knobs'!$B$15)+(F116*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F116))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G116*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C116+D116+(E116*'03 Mind Knobs'!$B$17)+(F116*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F116))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G116*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K116" t="n">
@@ -50527,7 +51658,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L116" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A116,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B116-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B116))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M116" t="n">
@@ -50569,11 +51700,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I117" t="n">
-        <x:f>--(MIN(1,C117+D117+(E117*'03 Mind Knobs'!$B$15)+(F117*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F117))&gt;=MAX(0.15,0.35+(G117*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C117+D117+(E117*'03 Mind Knobs'!$B$17)+(F117*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F117))&gt;=MAX(0.15,0.35+(G117*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J117" t="n">
-        <x:f>--(MIN(1,C117+D117+(E117*'03 Mind Knobs'!$B$15)+(F117*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F117))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G117*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C117+D117+(E117*'03 Mind Knobs'!$B$17)+(F117*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F117))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G117*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K117" t="n">
@@ -50581,7 +51712,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L117" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A117,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B117-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B117))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M117" t="n">
@@ -50623,11 +51754,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I118" t="n">
-        <x:f>--(MIN(1,C118+D118+(E118*'03 Mind Knobs'!$B$15)+(F118*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F118))&gt;=MAX(0.15,0.35+(G118*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C118+D118+(E118*'03 Mind Knobs'!$B$17)+(F118*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F118))&gt;=MAX(0.15,0.35+(G118*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J118" t="n">
-        <x:f>--(MIN(1,C118+D118+(E118*'03 Mind Knobs'!$B$15)+(F118*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F118))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G118*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C118+D118+(E118*'03 Mind Knobs'!$B$17)+(F118*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F118))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G118*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K118" t="n">
@@ -50635,7 +51766,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L118" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A118,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B118-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B118))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M118" t="n">
@@ -50677,11 +51808,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I119" t="n">
-        <x:f>--(MIN(1,C119+D119+(E119*'03 Mind Knobs'!$B$15)+(F119*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F119))&gt;=MAX(0.15,0.35+(G119*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C119+D119+(E119*'03 Mind Knobs'!$B$17)+(F119*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F119))&gt;=MAX(0.15,0.35+(G119*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J119" t="n">
-        <x:f>--(MIN(1,C119+D119+(E119*'03 Mind Knobs'!$B$15)+(F119*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F119))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G119*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C119+D119+(E119*'03 Mind Knobs'!$B$17)+(F119*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F119))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G119*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K119" t="n">
@@ -50689,7 +51820,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L119" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A119,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B119-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B119))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M119" t="n">
@@ -50731,11 +51862,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I120" t="n">
-        <x:f>--(MIN(1,C120+D120+(E120*'03 Mind Knobs'!$B$15)+(F120*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F120))&gt;=MAX(0.15,0.35+(G120*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C120+D120+(E120*'03 Mind Knobs'!$B$17)+(F120*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F120))&gt;=MAX(0.15,0.35+(G120*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J120" t="n">
-        <x:f>--(MIN(1,C120+D120+(E120*'03 Mind Knobs'!$B$15)+(F120*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F120))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G120*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C120+D120+(E120*'03 Mind Knobs'!$B$17)+(F120*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F120))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G120*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K120" t="n">
@@ -50743,7 +51874,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L120" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A120,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B120-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B120))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M120" t="n">
@@ -50785,11 +51916,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I121" t="n">
-        <x:f>--(MIN(1,C121+D121+(E121*'03 Mind Knobs'!$B$15)+(F121*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F121))&gt;=MAX(0.15,0.35+(G121*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C121+D121+(E121*'03 Mind Knobs'!$B$17)+(F121*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F121))&gt;=MAX(0.15,0.35+(G121*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J121" t="n">
-        <x:f>--(MIN(1,C121+D121+(E121*'03 Mind Knobs'!$B$15)+(F121*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F121))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G121*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C121+D121+(E121*'03 Mind Knobs'!$B$17)+(F121*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F121))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G121*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K121" t="n">
@@ -50797,7 +51928,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L121" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A121,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B121-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B121))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M121" t="n">
@@ -50839,11 +51970,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I122" t="n">
-        <x:f>--(MIN(1,C122+D122+(E122*'03 Mind Knobs'!$B$15)+(F122*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F122))&gt;=MAX(0.15,0.35+(G122*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C122+D122+(E122*'03 Mind Knobs'!$B$17)+(F122*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F122))&gt;=MAX(0.15,0.35+(G122*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J122" t="n">
-        <x:f>--(MIN(1,C122+D122+(E122*'03 Mind Knobs'!$B$15)+(F122*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F122))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G122*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C122+D122+(E122*'03 Mind Knobs'!$B$17)+(F122*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F122))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G122*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K122" t="n">
@@ -50851,7 +51982,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L122" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A122,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B122-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B122))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M122" t="n">
@@ -50893,11 +52024,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I123" t="n">
-        <x:f>--(MIN(1,C123+D123+(E123*'03 Mind Knobs'!$B$15)+(F123*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F123))&gt;=MAX(0.15,0.35+(G123*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C123+D123+(E123*'03 Mind Knobs'!$B$17)+(F123*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F123))&gt;=MAX(0.15,0.35+(G123*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J123" t="n">
-        <x:f>--(MIN(1,C123+D123+(E123*'03 Mind Knobs'!$B$15)+(F123*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F123))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G123*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C123+D123+(E123*'03 Mind Knobs'!$B$17)+(F123*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F123))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G123*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K123" t="n">
@@ -50905,7 +52036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L123" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A123,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B123-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B123))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M123" t="n">
@@ -50947,11 +52078,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I124" t="n">
-        <x:f>--(MIN(1,C124+D124+(E124*'03 Mind Knobs'!$B$15)+(F124*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F124))&gt;=MAX(0.15,0.35+(G124*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C124+D124+(E124*'03 Mind Knobs'!$B$17)+(F124*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F124))&gt;=MAX(0.15,0.35+(G124*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J124" t="n">
-        <x:f>--(MIN(1,C124+D124+(E124*'03 Mind Knobs'!$B$15)+(F124*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F124))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G124*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C124+D124+(E124*'03 Mind Knobs'!$B$17)+(F124*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F124))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G124*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K124" t="n">
@@ -50959,7 +52090,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L124" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A124,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B124-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B124))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M124" t="n">
@@ -51001,11 +52132,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I125" t="n">
-        <x:f>--(MIN(1,C125+D125+(E125*'03 Mind Knobs'!$B$15)+(F125*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F125))&gt;=MAX(0.15,0.35+(G125*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C125+D125+(E125*'03 Mind Knobs'!$B$17)+(F125*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F125))&gt;=MAX(0.15,0.35+(G125*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J125" t="n">
-        <x:f>--(MIN(1,C125+D125+(E125*'03 Mind Knobs'!$B$15)+(F125*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F125))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G125*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C125+D125+(E125*'03 Mind Knobs'!$B$17)+(F125*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F125))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G125*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K125" t="n">
@@ -51013,7 +52144,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L125" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A125,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B125-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B125))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M125" t="n">
@@ -51055,11 +52186,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I126" t="n">
-        <x:f>--(MIN(1,C126+D126+(E126*'03 Mind Knobs'!$B$15)+(F126*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F126))&gt;=MAX(0.15,0.35+(G126*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C126+D126+(E126*'03 Mind Knobs'!$B$17)+(F126*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F126))&gt;=MAX(0.15,0.35+(G126*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J126" t="n">
-        <x:f>--(MIN(1,C126+D126+(E126*'03 Mind Knobs'!$B$15)+(F126*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F126))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G126*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C126+D126+(E126*'03 Mind Knobs'!$B$17)+(F126*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F126))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G126*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K126" t="n">
@@ -51067,7 +52198,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L126" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A126,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B126-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B126))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M126" t="n">
@@ -51109,11 +52240,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I127" t="n">
-        <x:f>--(MIN(1,C127+D127+(E127*'03 Mind Knobs'!$B$15)+(F127*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F127))&gt;=MAX(0.15,0.35+(G127*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C127+D127+(E127*'03 Mind Knobs'!$B$17)+(F127*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F127))&gt;=MAX(0.15,0.35+(G127*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J127" t="n">
-        <x:f>--(MIN(1,C127+D127+(E127*'03 Mind Knobs'!$B$15)+(F127*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F127))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G127*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C127+D127+(E127*'03 Mind Knobs'!$B$17)+(F127*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F127))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G127*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K127" t="n">
@@ -51121,7 +52252,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L127" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A127,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B127-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B127))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M127" t="n">
@@ -51163,11 +52294,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I128" t="n">
-        <x:f>--(MIN(1,C128+D128+(E128*'03 Mind Knobs'!$B$15)+(F128*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F128))&gt;=MAX(0.15,0.35+(G128*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C128+D128+(E128*'03 Mind Knobs'!$B$17)+(F128*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F128))&gt;=MAX(0.15,0.35+(G128*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J128" t="n">
-        <x:f>--(MIN(1,C128+D128+(E128*'03 Mind Knobs'!$B$15)+(F128*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F128))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G128*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C128+D128+(E128*'03 Mind Knobs'!$B$17)+(F128*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F128))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G128*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K128" t="n">
@@ -51175,7 +52306,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L128" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A128,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B128-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B128))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M128" t="n">
@@ -51217,11 +52348,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I129" t="n">
-        <x:f>--(MIN(1,C129+D129+(E129*'03 Mind Knobs'!$B$15)+(F129*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F129))&gt;=MAX(0.15,0.35+(G129*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C129+D129+(E129*'03 Mind Knobs'!$B$17)+(F129*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F129))&gt;=MAX(0.15,0.35+(G129*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J129" t="n">
-        <x:f>--(MIN(1,C129+D129+(E129*'03 Mind Knobs'!$B$15)+(F129*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F129))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G129*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C129+D129+(E129*'03 Mind Knobs'!$B$17)+(F129*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F129))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G129*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K129" t="n">
@@ -51229,7 +52360,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L129" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A129,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B129-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B129))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M129" t="n">
@@ -51271,11 +52402,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I130" t="n">
-        <x:f>--(MIN(1,C130+D130+(E130*'03 Mind Knobs'!$B$15)+(F130*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F130))&gt;=MAX(0.15,0.35+(G130*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C130+D130+(E130*'03 Mind Knobs'!$B$17)+(F130*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F130))&gt;=MAX(0.15,0.35+(G130*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J130" t="n">
-        <x:f>--(MIN(1,C130+D130+(E130*'03 Mind Knobs'!$B$15)+(F130*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F130))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G130*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C130+D130+(E130*'03 Mind Knobs'!$B$17)+(F130*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F130))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G130*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K130" t="n">
@@ -51283,7 +52414,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L130" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A130,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B130-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B130))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M130" t="n">
@@ -51325,11 +52456,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I131" t="n">
-        <x:f>--(MIN(1,C131+D131+(E131*'03 Mind Knobs'!$B$15)+(F131*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F131))&gt;=MAX(0.15,0.35+(G131*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C131+D131+(E131*'03 Mind Knobs'!$B$17)+(F131*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F131))&gt;=MAX(0.15,0.35+(G131*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J131" t="n">
-        <x:f>--(MIN(1,C131+D131+(E131*'03 Mind Knobs'!$B$15)+(F131*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F131))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G131*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C131+D131+(E131*'03 Mind Knobs'!$B$17)+(F131*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F131))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G131*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K131" t="n">
@@ -51337,7 +52468,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L131" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A131,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B131-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B131))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M131" t="n">
@@ -51379,11 +52510,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I132" t="n">
-        <x:f>--(MIN(1,C132+D132+(E132*'03 Mind Knobs'!$B$15)+(F132*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F132))&gt;=MAX(0.15,0.35+(G132*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C132+D132+(E132*'03 Mind Knobs'!$B$17)+(F132*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F132))&gt;=MAX(0.15,0.35+(G132*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J132" t="n">
-        <x:f>--(MIN(1,C132+D132+(E132*'03 Mind Knobs'!$B$15)+(F132*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F132))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G132*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C132+D132+(E132*'03 Mind Knobs'!$B$17)+(F132*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F132))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G132*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K132" t="n">
@@ -51391,7 +52522,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L132" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A132,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B132-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B132))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M132" t="n">
@@ -51433,11 +52564,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I133" t="n">
-        <x:f>--(MIN(1,C133+D133+(E133*'03 Mind Knobs'!$B$15)+(F133*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F133))&gt;=MAX(0.15,0.35+(G133*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C133+D133+(E133*'03 Mind Knobs'!$B$17)+(F133*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F133))&gt;=MAX(0.15,0.35+(G133*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J133" t="n">
-        <x:f>--(MIN(1,C133+D133+(E133*'03 Mind Knobs'!$B$15)+(F133*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F133))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G133*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C133+D133+(E133*'03 Mind Knobs'!$B$17)+(F133*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F133))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G133*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K133" t="n">
@@ -51445,7 +52576,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L133" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A133,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B133-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B133))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M133" t="n">
@@ -51487,11 +52618,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I134" t="n">
-        <x:f>--(MIN(1,C134+D134+(E134*'03 Mind Knobs'!$B$15)+(F134*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F134))&gt;=MAX(0.15,0.35+(G134*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C134+D134+(E134*'03 Mind Knobs'!$B$17)+(F134*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F134))&gt;=MAX(0.15,0.35+(G134*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J134" t="n">
-        <x:f>--(MIN(1,C134+D134+(E134*'03 Mind Knobs'!$B$15)+(F134*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F134))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G134*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C134+D134+(E134*'03 Mind Knobs'!$B$17)+(F134*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F134))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G134*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K134" t="n">
@@ -51499,7 +52630,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L134" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A134,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B134-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B134))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M134" t="n">
@@ -51541,11 +52672,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I135" t="n">
-        <x:f>--(MIN(1,C135+D135+(E135*'03 Mind Knobs'!$B$15)+(F135*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F135))&gt;=MAX(0.15,0.35+(G135*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C135+D135+(E135*'03 Mind Knobs'!$B$17)+(F135*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F135))&gt;=MAX(0.15,0.35+(G135*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J135" t="n">
-        <x:f>--(MIN(1,C135+D135+(E135*'03 Mind Knobs'!$B$15)+(F135*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F135))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G135*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C135+D135+(E135*'03 Mind Knobs'!$B$17)+(F135*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F135))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G135*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K135" t="n">
@@ -51553,7 +52684,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L135" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A135,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B135-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B135))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M135" t="n">
@@ -51595,11 +52726,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I136" t="n">
-        <x:f>--(MIN(1,C136+D136+(E136*'03 Mind Knobs'!$B$15)+(F136*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F136))&gt;=MAX(0.15,0.35+(G136*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C136+D136+(E136*'03 Mind Knobs'!$B$17)+(F136*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F136))&gt;=MAX(0.15,0.35+(G136*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J136" t="n">
-        <x:f>--(MIN(1,C136+D136+(E136*'03 Mind Knobs'!$B$15)+(F136*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F136))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G136*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C136+D136+(E136*'03 Mind Knobs'!$B$17)+(F136*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F136))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G136*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K136" t="n">
@@ -51607,7 +52738,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L136" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A136,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B136-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B136))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M136" t="n">
@@ -51649,11 +52780,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I137" t="n">
-        <x:f>--(MIN(1,C137+D137+(E137*'03 Mind Knobs'!$B$15)+(F137*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F137))&gt;=MAX(0.15,0.35+(G137*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C137+D137+(E137*'03 Mind Knobs'!$B$17)+(F137*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F137))&gt;=MAX(0.15,0.35+(G137*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J137" t="n">
-        <x:f>--(MIN(1,C137+D137+(E137*'03 Mind Knobs'!$B$15)+(F137*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F137))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G137*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C137+D137+(E137*'03 Mind Knobs'!$B$17)+(F137*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F137))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G137*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K137" t="n">
@@ -51661,7 +52792,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L137" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A137,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B137-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B137))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M137" t="n">
@@ -51703,11 +52834,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I138" t="n">
-        <x:f>--(MIN(1,C138+D138+(E138*'03 Mind Knobs'!$B$15)+(F138*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F138))&gt;=MAX(0.15,0.35+(G138*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C138+D138+(E138*'03 Mind Knobs'!$B$17)+(F138*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F138))&gt;=MAX(0.15,0.35+(G138*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J138" t="n">
-        <x:f>--(MIN(1,C138+D138+(E138*'03 Mind Knobs'!$B$15)+(F138*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F138))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G138*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C138+D138+(E138*'03 Mind Knobs'!$B$17)+(F138*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F138))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G138*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K138" t="n">
@@ -51715,7 +52846,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L138" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A138,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B138-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B138))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M138" t="n">
@@ -51757,11 +52888,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I139" t="n">
-        <x:f>--(MIN(1,C139+D139+(E139*'03 Mind Knobs'!$B$15)+(F139*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F139))&gt;=MAX(0.15,0.35+(G139*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C139+D139+(E139*'03 Mind Knobs'!$B$17)+(F139*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F139))&gt;=MAX(0.15,0.35+(G139*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J139" t="n">
-        <x:f>--(MIN(1,C139+D139+(E139*'03 Mind Knobs'!$B$15)+(F139*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F139))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G139*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C139+D139+(E139*'03 Mind Knobs'!$B$17)+(F139*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F139))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G139*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K139" t="n">
@@ -51769,7 +52900,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L139" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A139,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B139-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B139))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M139" t="n">
@@ -51811,11 +52942,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I140" t="n">
-        <x:f>--(MIN(1,C140+D140+(E140*'03 Mind Knobs'!$B$15)+(F140*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F140))&gt;=MAX(0.15,0.35+(G140*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C140+D140+(E140*'03 Mind Knobs'!$B$17)+(F140*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F140))&gt;=MAX(0.15,0.35+(G140*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J140" t="n">
-        <x:f>--(MIN(1,C140+D140+(E140*'03 Mind Knobs'!$B$15)+(F140*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F140))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G140*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C140+D140+(E140*'03 Mind Knobs'!$B$17)+(F140*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F140))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G140*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K140" t="n">
@@ -51823,7 +52954,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L140" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A140,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B140-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B140))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M140" t="n">
@@ -51865,11 +52996,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I141" t="n">
-        <x:f>--(MIN(1,C141+D141+(E141*'03 Mind Knobs'!$B$15)+(F141*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F141))&gt;=MAX(0.15,0.35+(G141*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C141+D141+(E141*'03 Mind Knobs'!$B$17)+(F141*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F141))&gt;=MAX(0.15,0.35+(G141*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J141" t="n">
-        <x:f>--(MIN(1,C141+D141+(E141*'03 Mind Knobs'!$B$15)+(F141*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F141))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G141*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C141+D141+(E141*'03 Mind Knobs'!$B$17)+(F141*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F141))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G141*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K141" t="n">
@@ -51877,7 +53008,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L141" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A141,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B141-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B141))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M141" t="n">
@@ -51919,11 +53050,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I142" t="n">
-        <x:f>--(MIN(1,C142+D142+(E142*'03 Mind Knobs'!$B$15)+(F142*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F142))&gt;=MAX(0.15,0.35+(G142*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C142+D142+(E142*'03 Mind Knobs'!$B$17)+(F142*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F142))&gt;=MAX(0.15,0.35+(G142*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J142" t="n">
-        <x:f>--(MIN(1,C142+D142+(E142*'03 Mind Knobs'!$B$15)+(F142*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F142))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G142*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C142+D142+(E142*'03 Mind Knobs'!$B$17)+(F142*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F142))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G142*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K142" t="n">
@@ -51931,7 +53062,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L142" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A142,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B142-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B142))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M142" t="n">
@@ -51973,11 +53104,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I143" t="n">
-        <x:f>--(MIN(1,C143+D143+(E143*'03 Mind Knobs'!$B$15)+(F143*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F143))&gt;=MAX(0.15,0.35+(G143*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C143+D143+(E143*'03 Mind Knobs'!$B$17)+(F143*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F143))&gt;=MAX(0.15,0.35+(G143*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J143" t="n">
-        <x:f>--(MIN(1,C143+D143+(E143*'03 Mind Knobs'!$B$15)+(F143*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F143))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G143*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C143+D143+(E143*'03 Mind Knobs'!$B$17)+(F143*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F143))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G143*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K143" t="n">
@@ -51985,7 +53116,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L143" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A143,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B143-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B143))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M143" t="n">
@@ -52027,11 +53158,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I144" t="n">
-        <x:f>--(MIN(1,C144+D144+(E144*'03 Mind Knobs'!$B$15)+(F144*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F144))&gt;=MAX(0.15,0.35+(G144*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C144+D144+(E144*'03 Mind Knobs'!$B$17)+(F144*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F144))&gt;=MAX(0.15,0.35+(G144*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J144" t="n">
-        <x:f>--(MIN(1,C144+D144+(E144*'03 Mind Knobs'!$B$15)+(F144*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F144))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G144*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C144+D144+(E144*'03 Mind Knobs'!$B$17)+(F144*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F144))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G144*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K144" t="n">
@@ -52039,7 +53170,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L144" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A144,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B144-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B144))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M144" t="n">
@@ -52081,11 +53212,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I145" t="n">
-        <x:f>--(MIN(1,C145+D145+(E145*'03 Mind Knobs'!$B$15)+(F145*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F145))&gt;=MAX(0.15,0.35+(G145*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C145+D145+(E145*'03 Mind Knobs'!$B$17)+(F145*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F145))&gt;=MAX(0.15,0.35+(G145*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J145" t="n">
-        <x:f>--(MIN(1,C145+D145+(E145*'03 Mind Knobs'!$B$15)+(F145*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F145))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G145*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C145+D145+(E145*'03 Mind Knobs'!$B$17)+(F145*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F145))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G145*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K145" t="n">
@@ -52093,7 +53224,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L145" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A145,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B145-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B145))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M145" t="n">
@@ -52135,11 +53266,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I146" t="n">
-        <x:f>--(MIN(1,C146+D146+(E146*'03 Mind Knobs'!$B$15)+(F146*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F146))&gt;=MAX(0.15,0.35+(G146*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C146+D146+(E146*'03 Mind Knobs'!$B$17)+(F146*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F146))&gt;=MAX(0.15,0.35+(G146*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J146" t="n">
-        <x:f>--(MIN(1,C146+D146+(E146*'03 Mind Knobs'!$B$15)+(F146*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F146))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G146*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C146+D146+(E146*'03 Mind Knobs'!$B$17)+(F146*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F146))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G146*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K146" t="n">
@@ -52147,7 +53278,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L146" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A146,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B146-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B146))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M146" t="n">
@@ -52189,11 +53320,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I147" t="n">
-        <x:f>--(MIN(1,C147+D147+(E147*'03 Mind Knobs'!$B$15)+(F147*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F147))&gt;=MAX(0.15,0.35+(G147*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C147+D147+(E147*'03 Mind Knobs'!$B$17)+(F147*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F147))&gt;=MAX(0.15,0.35+(G147*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J147" t="n">
-        <x:f>--(MIN(1,C147+D147+(E147*'03 Mind Knobs'!$B$15)+(F147*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F147))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G147*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C147+D147+(E147*'03 Mind Knobs'!$B$17)+(F147*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F147))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G147*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K147" t="n">
@@ -52201,7 +53332,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L147" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A147,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B147-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B147))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M147" t="n">
@@ -52243,11 +53374,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I148" t="n">
-        <x:f>--(MIN(1,C148+D148+(E148*'03 Mind Knobs'!$B$15)+(F148*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F148))&gt;=MAX(0.15,0.35+(G148*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C148+D148+(E148*'03 Mind Knobs'!$B$17)+(F148*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F148))&gt;=MAX(0.15,0.35+(G148*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J148" t="n">
-        <x:f>--(MIN(1,C148+D148+(E148*'03 Mind Knobs'!$B$15)+(F148*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F148))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G148*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C148+D148+(E148*'03 Mind Knobs'!$B$17)+(F148*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F148))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G148*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K148" t="n">
@@ -52255,7 +53386,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L148" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A148,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B148-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B148))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M148" t="n">
@@ -52297,11 +53428,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I149" t="n">
-        <x:f>--(MIN(1,C149+D149+(E149*'03 Mind Knobs'!$B$15)+(F149*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F149))&gt;=MAX(0.15,0.35+(G149*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C149+D149+(E149*'03 Mind Knobs'!$B$17)+(F149*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F149))&gt;=MAX(0.15,0.35+(G149*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J149" t="n">
-        <x:f>--(MIN(1,C149+D149+(E149*'03 Mind Knobs'!$B$15)+(F149*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F149))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G149*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C149+D149+(E149*'03 Mind Knobs'!$B$17)+(F149*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F149))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G149*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K149" t="n">
@@ -52309,7 +53440,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L149" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A149,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B149-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B149))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M149" t="n">
@@ -52351,11 +53482,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I150" t="n">
-        <x:f>--(MIN(1,C150+D150+(E150*'03 Mind Knobs'!$B$15)+(F150*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F150))&gt;=MAX(0.15,0.35+(G150*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C150+D150+(E150*'03 Mind Knobs'!$B$17)+(F150*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F150))&gt;=MAX(0.15,0.35+(G150*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J150" t="n">
-        <x:f>--(MIN(1,C150+D150+(E150*'03 Mind Knobs'!$B$15)+(F150*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F150))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G150*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C150+D150+(E150*'03 Mind Knobs'!$B$17)+(F150*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F150))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G150*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K150" t="n">
@@ -52363,7 +53494,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L150" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A150,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B150-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B150))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M150" t="n">
@@ -52405,11 +53536,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I151" t="n">
-        <x:f>--(MIN(1,C151+D151+(E151*'03 Mind Knobs'!$B$15)+(F151*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F151))&gt;=MAX(0.15,0.35+(G151*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C151+D151+(E151*'03 Mind Knobs'!$B$17)+(F151*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F151))&gt;=MAX(0.15,0.35+(G151*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J151" t="n">
-        <x:f>--(MIN(1,C151+D151+(E151*'03 Mind Knobs'!$B$15)+(F151*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F151))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G151*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C151+D151+(E151*'03 Mind Knobs'!$B$17)+(F151*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F151))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G151*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K151" t="n">
@@ -52417,7 +53548,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L151" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A151,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B151-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B151))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M151" t="n">
@@ -52459,11 +53590,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I152" t="n">
-        <x:f>--(MIN(1,C152+D152+(E152*'03 Mind Knobs'!$B$15)+(F152*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F152))&gt;=MAX(0.15,0.35+(G152*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C152+D152+(E152*'03 Mind Knobs'!$B$17)+(F152*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F152))&gt;=MAX(0.15,0.35+(G152*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J152" t="n">
-        <x:f>--(MIN(1,C152+D152+(E152*'03 Mind Knobs'!$B$15)+(F152*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F152))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G152*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C152+D152+(E152*'03 Mind Knobs'!$B$17)+(F152*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F152))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G152*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K152" t="n">
@@ -52471,7 +53602,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L152" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A152,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B152-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B152))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M152" t="n">
@@ -52513,11 +53644,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I153" t="n">
-        <x:f>--(MIN(1,C153+D153+(E153*'03 Mind Knobs'!$B$15)+(F153*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F153))&gt;=MAX(0.15,0.35+(G153*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C153+D153+(E153*'03 Mind Knobs'!$B$17)+(F153*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F153))&gt;=MAX(0.15,0.35+(G153*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J153" t="n">
-        <x:f>--(MIN(1,C153+D153+(E153*'03 Mind Knobs'!$B$15)+(F153*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F153))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G153*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C153+D153+(E153*'03 Mind Knobs'!$B$17)+(F153*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F153))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G153*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K153" t="n">
@@ -52525,7 +53656,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L153" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A153,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B153-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B153))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M153" t="n">
@@ -52567,11 +53698,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I154" t="n">
-        <x:f>--(MIN(1,C154+D154+(E154*'03 Mind Knobs'!$B$15)+(F154*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F154))&gt;=MAX(0.15,0.35+(G154*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C154+D154+(E154*'03 Mind Knobs'!$B$17)+(F154*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F154))&gt;=MAX(0.15,0.35+(G154*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J154" t="n">
-        <x:f>--(MIN(1,C154+D154+(E154*'03 Mind Knobs'!$B$15)+(F154*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F154))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G154*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C154+D154+(E154*'03 Mind Knobs'!$B$17)+(F154*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F154))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G154*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K154" t="n">
@@ -52579,7 +53710,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L154" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A154,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B154-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B154))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M154" t="n">
@@ -52621,11 +53752,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I155" t="n">
-        <x:f>--(MIN(1,C155+D155+(E155*'03 Mind Knobs'!$B$15)+(F155*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F155))&gt;=MAX(0.15,0.35+(G155*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C155+D155+(E155*'03 Mind Knobs'!$B$17)+(F155*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F155))&gt;=MAX(0.15,0.35+(G155*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J155" t="n">
-        <x:f>--(MIN(1,C155+D155+(E155*'03 Mind Knobs'!$B$15)+(F155*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F155))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G155*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C155+D155+(E155*'03 Mind Knobs'!$B$17)+(F155*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F155))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G155*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K155" t="n">
@@ -52633,7 +53764,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L155" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A155,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B155-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B155))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M155" t="n">
@@ -52675,11 +53806,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I156" t="n">
-        <x:f>--(MIN(1,C156+D156+(E156*'03 Mind Knobs'!$B$15)+(F156*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F156))&gt;=MAX(0.15,0.35+(G156*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C156+D156+(E156*'03 Mind Knobs'!$B$17)+(F156*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F156))&gt;=MAX(0.15,0.35+(G156*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J156" t="n">
-        <x:f>--(MIN(1,C156+D156+(E156*'03 Mind Knobs'!$B$15)+(F156*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F156))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G156*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C156+D156+(E156*'03 Mind Knobs'!$B$17)+(F156*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F156))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G156*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K156" t="n">
@@ -52687,7 +53818,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L156" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A156,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B156-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B156))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M156" t="n">
@@ -52729,11 +53860,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I157" t="n">
-        <x:f>--(MIN(1,C157+D157+(E157*'03 Mind Knobs'!$B$15)+(F157*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F157))&gt;=MAX(0.15,0.35+(G157*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C157+D157+(E157*'03 Mind Knobs'!$B$17)+(F157*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F157))&gt;=MAX(0.15,0.35+(G157*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J157" t="n">
-        <x:f>--(MIN(1,C157+D157+(E157*'03 Mind Knobs'!$B$15)+(F157*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F157))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G157*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C157+D157+(E157*'03 Mind Knobs'!$B$17)+(F157*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F157))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G157*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K157" t="n">
@@ -52741,7 +53872,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L157" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A157,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B157-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B157))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M157" t="n">
@@ -52783,11 +53914,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I158" t="n">
-        <x:f>--(MIN(1,C158+D158+(E158*'03 Mind Knobs'!$B$15)+(F158*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F158))&gt;=MAX(0.15,0.35+(G158*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C158+D158+(E158*'03 Mind Knobs'!$B$17)+(F158*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F158))&gt;=MAX(0.15,0.35+(G158*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J158" t="n">
-        <x:f>--(MIN(1,C158+D158+(E158*'03 Mind Knobs'!$B$15)+(F158*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F158))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G158*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C158+D158+(E158*'03 Mind Knobs'!$B$17)+(F158*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F158))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G158*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K158" t="n">
@@ -52795,7 +53926,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L158" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A158,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B158-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B158))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M158" t="n">
@@ -52837,11 +53968,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I159" t="n">
-        <x:f>--(MIN(1,C159+D159+(E159*'03 Mind Knobs'!$B$15)+(F159*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F159))&gt;=MAX(0.15,0.35+(G159*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C159+D159+(E159*'03 Mind Knobs'!$B$17)+(F159*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F159))&gt;=MAX(0.15,0.35+(G159*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J159" t="n">
-        <x:f>--(MIN(1,C159+D159+(E159*'03 Mind Knobs'!$B$15)+(F159*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F159))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G159*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C159+D159+(E159*'03 Mind Knobs'!$B$17)+(F159*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F159))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G159*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K159" t="n">
@@ -52849,7 +53980,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L159" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A159,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B159-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B159))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M159" t="n">
@@ -52891,11 +54022,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I160" t="n">
-        <x:f>--(MIN(1,C160+D160+(E160*'03 Mind Knobs'!$B$15)+(F160*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F160))&gt;=MAX(0.15,0.35+(G160*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C160+D160+(E160*'03 Mind Knobs'!$B$17)+(F160*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F160))&gt;=MAX(0.15,0.35+(G160*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J160" t="n">
-        <x:f>--(MIN(1,C160+D160+(E160*'03 Mind Knobs'!$B$15)+(F160*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F160))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G160*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C160+D160+(E160*'03 Mind Knobs'!$B$17)+(F160*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F160))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G160*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K160" t="n">
@@ -52903,7 +54034,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L160" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A160,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B160-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B160))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M160" t="n">
@@ -52945,11 +54076,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I161" t="n">
-        <x:f>--(MIN(1,C161+D161+(E161*'03 Mind Knobs'!$B$15)+(F161*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F161))&gt;=MAX(0.15,0.35+(G161*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C161+D161+(E161*'03 Mind Knobs'!$B$17)+(F161*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F161))&gt;=MAX(0.15,0.35+(G161*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J161" t="n">
-        <x:f>--(MIN(1,C161+D161+(E161*'03 Mind Knobs'!$B$15)+(F161*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F161))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G161*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C161+D161+(E161*'03 Mind Knobs'!$B$17)+(F161*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F161))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G161*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K161" t="n">
@@ -52957,7 +54088,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L161" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A161,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B161-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B161))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M161" t="n">
@@ -52999,11 +54130,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I162" t="n">
-        <x:f>--(MIN(1,C162+D162+(E162*'03 Mind Knobs'!$B$15)+(F162*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F162))&gt;=MAX(0.15,0.35+(G162*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C162+D162+(E162*'03 Mind Knobs'!$B$17)+(F162*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F162))&gt;=MAX(0.15,0.35+(G162*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J162" t="n">
-        <x:f>--(MIN(1,C162+D162+(E162*'03 Mind Knobs'!$B$15)+(F162*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F162))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G162*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C162+D162+(E162*'03 Mind Knobs'!$B$17)+(F162*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F162))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G162*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K162" t="n">
@@ -53011,7 +54142,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L162" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A162,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B162-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B162))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M162" t="n">
@@ -53053,11 +54184,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I163" t="n">
-        <x:f>--(MIN(1,C163+D163+(E163*'03 Mind Knobs'!$B$15)+(F163*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F163))&gt;=MAX(0.15,0.35+(G163*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C163+D163+(E163*'03 Mind Knobs'!$B$17)+(F163*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F163))&gt;=MAX(0.15,0.35+(G163*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J163" t="n">
-        <x:f>--(MIN(1,C163+D163+(E163*'03 Mind Knobs'!$B$15)+(F163*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F163))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G163*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C163+D163+(E163*'03 Mind Knobs'!$B$17)+(F163*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F163))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G163*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K163" t="n">
@@ -53065,7 +54196,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L163" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A163,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B163-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B163))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M163" t="n">
@@ -53107,11 +54238,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I164" t="n">
-        <x:f>--(MIN(1,C164+D164+(E164*'03 Mind Knobs'!$B$15)+(F164*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F164))&gt;=MAX(0.15,0.35+(G164*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C164+D164+(E164*'03 Mind Knobs'!$B$17)+(F164*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F164))&gt;=MAX(0.15,0.35+(G164*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J164" t="n">
-        <x:f>--(MIN(1,C164+D164+(E164*'03 Mind Knobs'!$B$15)+(F164*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F164))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G164*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C164+D164+(E164*'03 Mind Knobs'!$B$17)+(F164*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F164))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G164*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K164" t="n">
@@ -53119,7 +54250,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L164" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A164,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B164-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B164))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M164" t="n">
@@ -53161,11 +54292,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I165" t="n">
-        <x:f>--(MIN(1,C165+D165+(E165*'03 Mind Knobs'!$B$15)+(F165*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F165))&gt;=MAX(0.15,0.35+(G165*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C165+D165+(E165*'03 Mind Knobs'!$B$17)+(F165*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F165))&gt;=MAX(0.15,0.35+(G165*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J165" t="n">
-        <x:f>--(MIN(1,C165+D165+(E165*'03 Mind Knobs'!$B$15)+(F165*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F165))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G165*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C165+D165+(E165*'03 Mind Knobs'!$B$17)+(F165*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F165))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G165*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K165" t="n">
@@ -53173,7 +54304,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L165" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A165,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B165-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B165))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M165" t="n">
@@ -53215,11 +54346,11 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I166" t="n">
-        <x:f>--(MIN(1,C166+D166+(E166*'03 Mind Knobs'!$B$15)+(F166*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F166))&gt;=MAX(0.15,0.35+(G166*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C166+D166+(E166*'03 Mind Knobs'!$B$17)+(F166*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F166))&gt;=MAX(0.15,0.35+(G166*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J166" t="n">
-        <x:f>--(MIN(1,C166+D166+(E166*'03 Mind Knobs'!$B$15)+(F166*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F166))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G166*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C166+D166+(E166*'03 Mind Knobs'!$B$17)+(F166*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F166))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G166*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K166" t="n">
@@ -53227,7 +54358,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L166" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A166,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B166-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B166))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M166" t="n">
@@ -53269,11 +54400,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I167" t="n">
-        <x:f>--(MIN(1,C167+D167+(E167*'03 Mind Knobs'!$B$15)+(F167*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F167))&gt;=MAX(0.15,0.35+(G167*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C167+D167+(E167*'03 Mind Knobs'!$B$17)+(F167*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F167))&gt;=MAX(0.15,0.35+(G167*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J167" t="n">
-        <x:f>--(MIN(1,C167+D167+(E167*'03 Mind Knobs'!$B$15)+(F167*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F167))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G167*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C167+D167+(E167*'03 Mind Knobs'!$B$17)+(F167*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F167))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G167*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K167" t="n">
@@ -53281,7 +54412,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L167" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A167,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B167-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B167))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M167" t="n">
@@ -53323,11 +54454,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I168" t="n">
-        <x:f>--(MIN(1,C168+D168+(E168*'03 Mind Knobs'!$B$15)+(F168*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F168))&gt;=MAX(0.15,0.35+(G168*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C168+D168+(E168*'03 Mind Knobs'!$B$17)+(F168*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F168))&gt;=MAX(0.15,0.35+(G168*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J168" t="n">
-        <x:f>--(MIN(1,C168+D168+(E168*'03 Mind Knobs'!$B$15)+(F168*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F168))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G168*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C168+D168+(E168*'03 Mind Knobs'!$B$17)+(F168*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F168))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G168*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K168" t="n">
@@ -53335,7 +54466,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L168" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A168,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B168-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B168))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M168" t="n">
@@ -53377,11 +54508,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I169" t="n">
-        <x:f>--(MIN(1,C169+D169+(E169*'03 Mind Knobs'!$B$15)+(F169*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F169))&gt;=MAX(0.15,0.35+(G169*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C169+D169+(E169*'03 Mind Knobs'!$B$17)+(F169*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F169))&gt;=MAX(0.15,0.35+(G169*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J169" t="n">
-        <x:f>--(MIN(1,C169+D169+(E169*'03 Mind Knobs'!$B$15)+(F169*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F169))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G169*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C169+D169+(E169*'03 Mind Knobs'!$B$17)+(F169*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F169))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G169*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K169" t="n">
@@ -53389,7 +54520,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L169" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A169,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B169-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B169))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M169" t="n">
@@ -53431,11 +54562,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I170" t="n">
-        <x:f>--(MIN(1,C170+D170+(E170*'03 Mind Knobs'!$B$15)+(F170*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F170))&gt;=MAX(0.15,0.35+(G170*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C170+D170+(E170*'03 Mind Knobs'!$B$17)+(F170*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F170))&gt;=MAX(0.15,0.35+(G170*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J170" t="n">
-        <x:f>--(MIN(1,C170+D170+(E170*'03 Mind Knobs'!$B$15)+(F170*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F170))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G170*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C170+D170+(E170*'03 Mind Knobs'!$B$17)+(F170*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F170))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G170*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K170" t="n">
@@ -53443,7 +54574,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L170" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A170,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B170-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B170))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M170" t="n">
@@ -53485,11 +54616,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I171" t="n">
-        <x:f>--(MIN(1,C171+D171+(E171*'03 Mind Knobs'!$B$15)+(F171*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F171))&gt;=MAX(0.15,0.35+(G171*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C171+D171+(E171*'03 Mind Knobs'!$B$17)+(F171*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F171))&gt;=MAX(0.15,0.35+(G171*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J171" t="n">
-        <x:f>--(MIN(1,C171+D171+(E171*'03 Mind Knobs'!$B$15)+(F171*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F171))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G171*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C171+D171+(E171*'03 Mind Knobs'!$B$17)+(F171*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F171))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G171*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K171" t="n">
@@ -53497,7 +54628,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L171" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A171,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B171-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B171))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M171" t="n">
@@ -53539,11 +54670,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I172" t="n">
-        <x:f>--(MIN(1,C172+D172+(E172*'03 Mind Knobs'!$B$15)+(F172*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F172))&gt;=MAX(0.15,0.35+(G172*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C172+D172+(E172*'03 Mind Knobs'!$B$17)+(F172*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F172))&gt;=MAX(0.15,0.35+(G172*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J172" t="n">
-        <x:f>--(MIN(1,C172+D172+(E172*'03 Mind Knobs'!$B$15)+(F172*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F172))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G172*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C172+D172+(E172*'03 Mind Knobs'!$B$17)+(F172*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F172))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G172*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K172" t="n">
@@ -53551,7 +54682,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L172" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A172,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B172-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B172))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M172" t="n">
@@ -53593,11 +54724,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I173" t="n">
-        <x:f>--(MIN(1,C173+D173+(E173*'03 Mind Knobs'!$B$15)+(F173*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F173))&gt;=MAX(0.15,0.35+(G173*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C173+D173+(E173*'03 Mind Knobs'!$B$17)+(F173*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F173))&gt;=MAX(0.15,0.35+(G173*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J173" t="n">
-        <x:f>--(MIN(1,C173+D173+(E173*'03 Mind Knobs'!$B$15)+(F173*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F173))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G173*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C173+D173+(E173*'03 Mind Knobs'!$B$17)+(F173*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F173))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G173*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K173" t="n">
@@ -53605,7 +54736,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L173" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A173,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B173-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B173))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M173" t="n">
@@ -53647,11 +54778,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I174" t="n">
-        <x:f>--(MIN(1,C174+D174+(E174*'03 Mind Knobs'!$B$15)+(F174*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F174))&gt;=MAX(0.15,0.35+(G174*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C174+D174+(E174*'03 Mind Knobs'!$B$17)+(F174*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F174))&gt;=MAX(0.15,0.35+(G174*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J174" t="n">
-        <x:f>--(MIN(1,C174+D174+(E174*'03 Mind Knobs'!$B$15)+(F174*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F174))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G174*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C174+D174+(E174*'03 Mind Knobs'!$B$17)+(F174*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F174))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G174*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K174" t="n">
@@ -53659,7 +54790,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L174" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A174,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B174-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B174))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M174" t="n">
@@ -53701,11 +54832,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I175" t="n">
-        <x:f>--(MIN(1,C175+D175+(E175*'03 Mind Knobs'!$B$15)+(F175*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F175))&gt;=MAX(0.15,0.35+(G175*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C175+D175+(E175*'03 Mind Knobs'!$B$17)+(F175*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F175))&gt;=MAX(0.15,0.35+(G175*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J175" t="n">
-        <x:f>--(MIN(1,C175+D175+(E175*'03 Mind Knobs'!$B$15)+(F175*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F175))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G175*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C175+D175+(E175*'03 Mind Knobs'!$B$17)+(F175*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F175))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G175*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K175" t="n">
@@ -53713,7 +54844,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L175" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A175,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B175-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B175))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M175" t="n">
@@ -53755,11 +54886,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I176" t="n">
-        <x:f>--(MIN(1,C176+D176+(E176*'03 Mind Knobs'!$B$15)+(F176*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F176))&gt;=MAX(0.15,0.35+(G176*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C176+D176+(E176*'03 Mind Knobs'!$B$17)+(F176*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F176))&gt;=MAX(0.15,0.35+(G176*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J176" t="n">
-        <x:f>--(MIN(1,C176+D176+(E176*'03 Mind Knobs'!$B$15)+(F176*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F176))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G176*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C176+D176+(E176*'03 Mind Knobs'!$B$17)+(F176*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F176))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G176*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K176" t="n">
@@ -53767,7 +54898,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L176" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A176,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B176-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B176))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M176" t="n">
@@ -53809,11 +54940,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I177" t="n">
-        <x:f>--(MIN(1,C177+D177+(E177*'03 Mind Knobs'!$B$15)+(F177*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F177))&gt;=MAX(0.15,0.35+(G177*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C177+D177+(E177*'03 Mind Knobs'!$B$17)+(F177*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F177))&gt;=MAX(0.15,0.35+(G177*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J177" t="n">
-        <x:f>--(MIN(1,C177+D177+(E177*'03 Mind Knobs'!$B$15)+(F177*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F177))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G177*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C177+D177+(E177*'03 Mind Knobs'!$B$17)+(F177*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F177))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G177*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K177" t="n">
@@ -53821,7 +54952,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L177" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A177,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B177-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B177))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M177" t="n">
@@ -53863,11 +54994,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I178" t="n">
-        <x:f>--(MIN(1,C178+D178+(E178*'03 Mind Knobs'!$B$15)+(F178*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F178))&gt;=MAX(0.15,0.35+(G178*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C178+D178+(E178*'03 Mind Knobs'!$B$17)+(F178*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F178))&gt;=MAX(0.15,0.35+(G178*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J178" t="n">
-        <x:f>--(MIN(1,C178+D178+(E178*'03 Mind Knobs'!$B$15)+(F178*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F178))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G178*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C178+D178+(E178*'03 Mind Knobs'!$B$17)+(F178*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F178))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G178*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K178" t="n">
@@ -53875,7 +55006,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L178" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A178,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B178-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B178))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M178" t="n">
@@ -53917,11 +55048,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I179" t="n">
-        <x:f>--(MIN(1,C179+D179+(E179*'03 Mind Knobs'!$B$15)+(F179*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F179))&gt;=MAX(0.15,0.35+(G179*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C179+D179+(E179*'03 Mind Knobs'!$B$17)+(F179*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F179))&gt;=MAX(0.15,0.35+(G179*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J179" t="n">
-        <x:f>--(MIN(1,C179+D179+(E179*'03 Mind Knobs'!$B$15)+(F179*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F179))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G179*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C179+D179+(E179*'03 Mind Knobs'!$B$17)+(F179*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F179))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G179*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K179" t="n">
@@ -53929,7 +55060,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L179" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A179,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B179-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B179))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M179" t="n">
@@ -53971,11 +55102,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I180" t="n">
-        <x:f>--(MIN(1,C180+D180+(E180*'03 Mind Knobs'!$B$15)+(F180*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F180))&gt;=MAX(0.15,0.35+(G180*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C180+D180+(E180*'03 Mind Knobs'!$B$17)+(F180*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F180))&gt;=MAX(0.15,0.35+(G180*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J180" t="n">
-        <x:f>--(MIN(1,C180+D180+(E180*'03 Mind Knobs'!$B$15)+(F180*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F180))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G180*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C180+D180+(E180*'03 Mind Knobs'!$B$17)+(F180*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F180))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G180*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K180" t="n">
@@ -53983,7 +55114,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L180" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A180,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B180-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B180))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M180" t="n">
@@ -54025,11 +55156,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I181" t="n">
-        <x:f>--(MIN(1,C181+D181+(E181*'03 Mind Knobs'!$B$15)+(F181*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F181))&gt;=MAX(0.15,0.35+(G181*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C181+D181+(E181*'03 Mind Knobs'!$B$17)+(F181*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F181))&gt;=MAX(0.15,0.35+(G181*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J181" t="n">
-        <x:f>--(MIN(1,C181+D181+(E181*'03 Mind Knobs'!$B$15)+(F181*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F181))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G181*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C181+D181+(E181*'03 Mind Knobs'!$B$17)+(F181*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F181))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G181*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K181" t="n">
@@ -54037,7 +55168,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L181" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A181,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B181-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B181))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M181" t="n">
@@ -54079,11 +55210,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I182" t="n">
-        <x:f>--(MIN(1,C182+D182+(E182*'03 Mind Knobs'!$B$15)+(F182*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F182))&gt;=MAX(0.15,0.35+(G182*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C182+D182+(E182*'03 Mind Knobs'!$B$17)+(F182*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F182))&gt;=MAX(0.15,0.35+(G182*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J182" t="n">
-        <x:f>--(MIN(1,C182+D182+(E182*'03 Mind Knobs'!$B$15)+(F182*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F182))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G182*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C182+D182+(E182*'03 Mind Knobs'!$B$17)+(F182*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F182))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G182*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K182" t="n">
@@ -54091,7 +55222,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L182" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A182,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B182-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B182))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M182" t="n">
@@ -54133,11 +55264,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I183" t="n">
-        <x:f>--(MIN(1,C183+D183+(E183*'03 Mind Knobs'!$B$15)+(F183*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F183))&gt;=MAX(0.15,0.35+(G183*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C183+D183+(E183*'03 Mind Knobs'!$B$17)+(F183*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F183))&gt;=MAX(0.15,0.35+(G183*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J183" t="n">
-        <x:f>--(MIN(1,C183+D183+(E183*'03 Mind Knobs'!$B$15)+(F183*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F183))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G183*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C183+D183+(E183*'03 Mind Knobs'!$B$17)+(F183*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F183))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G183*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K183" t="n">
@@ -54145,7 +55276,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L183" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A183,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B183-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B183))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M183" t="n">
@@ -54187,11 +55318,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I184" t="n">
-        <x:f>--(MIN(1,C184+D184+(E184*'03 Mind Knobs'!$B$15)+(F184*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F184))&gt;=MAX(0.15,0.35+(G184*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C184+D184+(E184*'03 Mind Knobs'!$B$17)+(F184*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F184))&gt;=MAX(0.15,0.35+(G184*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J184" t="n">
-        <x:f>--(MIN(1,C184+D184+(E184*'03 Mind Knobs'!$B$15)+(F184*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F184))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G184*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C184+D184+(E184*'03 Mind Knobs'!$B$17)+(F184*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F184))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G184*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K184" t="n">
@@ -54199,7 +55330,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L184" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A184,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B184-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B184))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M184" t="n">
@@ -54241,11 +55372,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I185" t="n">
-        <x:f>--(MIN(1,C185+D185+(E185*'03 Mind Knobs'!$B$15)+(F185*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F185))&gt;=MAX(0.15,0.35+(G185*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C185+D185+(E185*'03 Mind Knobs'!$B$17)+(F185*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F185))&gt;=MAX(0.15,0.35+(G185*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J185" t="n">
-        <x:f>--(MIN(1,C185+D185+(E185*'03 Mind Knobs'!$B$15)+(F185*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F185))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G185*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C185+D185+(E185*'03 Mind Knobs'!$B$17)+(F185*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F185))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G185*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K185" t="n">
@@ -54253,7 +55384,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L185" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A185,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B185-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B185))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M185" t="n">
@@ -54295,11 +55426,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I186" t="n">
-        <x:f>--(MIN(1,C186+D186+(E186*'03 Mind Knobs'!$B$15)+(F186*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F186))&gt;=MAX(0.15,0.35+(G186*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C186+D186+(E186*'03 Mind Knobs'!$B$17)+(F186*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F186))&gt;=MAX(0.15,0.35+(G186*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J186" t="n">
-        <x:f>--(MIN(1,C186+D186+(E186*'03 Mind Knobs'!$B$15)+(F186*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F186))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G186*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C186+D186+(E186*'03 Mind Knobs'!$B$17)+(F186*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F186))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G186*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K186" t="n">
@@ -54307,7 +55438,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L186" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A186,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B186-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B186))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M186" t="n">
@@ -54349,11 +55480,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I187" t="n">
-        <x:f>--(MIN(1,C187+D187+(E187*'03 Mind Knobs'!$B$15)+(F187*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F187))&gt;=MAX(0.15,0.35+(G187*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C187+D187+(E187*'03 Mind Knobs'!$B$17)+(F187*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F187))&gt;=MAX(0.15,0.35+(G187*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J187" t="n">
-        <x:f>--(MIN(1,C187+D187+(E187*'03 Mind Knobs'!$B$15)+(F187*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F187))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G187*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C187+D187+(E187*'03 Mind Knobs'!$B$17)+(F187*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F187))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G187*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K187" t="n">
@@ -54361,7 +55492,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L187" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A187,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B187-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B187))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M187" t="n">
@@ -54403,11 +55534,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I188" t="n">
-        <x:f>--(MIN(1,C188+D188+(E188*'03 Mind Knobs'!$B$15)+(F188*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F188))&gt;=MAX(0.15,0.35+(G188*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C188+D188+(E188*'03 Mind Knobs'!$B$17)+(F188*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F188))&gt;=MAX(0.15,0.35+(G188*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J188" t="n">
-        <x:f>--(MIN(1,C188+D188+(E188*'03 Mind Knobs'!$B$15)+(F188*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F188))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G188*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C188+D188+(E188*'03 Mind Knobs'!$B$17)+(F188*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F188))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G188*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K188" t="n">
@@ -54415,7 +55546,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L188" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A188,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B188-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B188))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M188" t="n">
@@ -54457,11 +55588,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I189" t="n">
-        <x:f>--(MIN(1,C189+D189+(E189*'03 Mind Knobs'!$B$15)+(F189*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F189))&gt;=MAX(0.15,0.35+(G189*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C189+D189+(E189*'03 Mind Knobs'!$B$17)+(F189*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F189))&gt;=MAX(0.15,0.35+(G189*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J189" t="n">
-        <x:f>--(MIN(1,C189+D189+(E189*'03 Mind Knobs'!$B$15)+(F189*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F189))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G189*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C189+D189+(E189*'03 Mind Knobs'!$B$17)+(F189*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F189))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G189*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K189" t="n">
@@ -54469,7 +55600,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L189" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A189,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B189-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B189))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M189" t="n">
@@ -54511,11 +55642,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I190" t="n">
-        <x:f>--(MIN(1,C190+D190+(E190*'03 Mind Knobs'!$B$15)+(F190*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F190))&gt;=MAX(0.15,0.35+(G190*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C190+D190+(E190*'03 Mind Knobs'!$B$17)+(F190*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F190))&gt;=MAX(0.15,0.35+(G190*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J190" t="n">
-        <x:f>--(MIN(1,C190+D190+(E190*'03 Mind Knobs'!$B$15)+(F190*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F190))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G190*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C190+D190+(E190*'03 Mind Knobs'!$B$17)+(F190*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F190))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G190*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K190" t="n">
@@ -54523,7 +55654,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L190" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A190,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B190-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B190))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M190" t="n">
@@ -54565,11 +55696,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I191" t="n">
-        <x:f>--(MIN(1,C191+D191+(E191*'03 Mind Knobs'!$B$15)+(F191*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F191))&gt;=MAX(0.15,0.35+(G191*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C191+D191+(E191*'03 Mind Knobs'!$B$17)+(F191*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F191))&gt;=MAX(0.15,0.35+(G191*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J191" t="n">
-        <x:f>--(MIN(1,C191+D191+(E191*'03 Mind Knobs'!$B$15)+(F191*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F191))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G191*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C191+D191+(E191*'03 Mind Knobs'!$B$17)+(F191*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F191))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G191*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K191" t="n">
@@ -54577,7 +55708,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L191" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A191,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B191-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B191))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M191" t="n">
@@ -54619,11 +55750,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I192" t="n">
-        <x:f>--(MIN(1,C192+D192+(E192*'03 Mind Knobs'!$B$15)+(F192*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F192))&gt;=MAX(0.15,0.35+(G192*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C192+D192+(E192*'03 Mind Knobs'!$B$17)+(F192*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F192))&gt;=MAX(0.15,0.35+(G192*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J192" t="n">
-        <x:f>--(MIN(1,C192+D192+(E192*'03 Mind Knobs'!$B$15)+(F192*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F192))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G192*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C192+D192+(E192*'03 Mind Knobs'!$B$17)+(F192*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F192))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G192*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K192" t="n">
@@ -54631,7 +55762,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L192" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A192,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B192-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B192))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M192" t="n">
@@ -54673,11 +55804,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I193" t="n">
-        <x:f>--(MIN(1,C193+D193+(E193*'03 Mind Knobs'!$B$15)+(F193*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F193))&gt;=MAX(0.15,0.35+(G193*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C193+D193+(E193*'03 Mind Knobs'!$B$17)+(F193*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F193))&gt;=MAX(0.15,0.35+(G193*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J193" t="n">
-        <x:f>--(MIN(1,C193+D193+(E193*'03 Mind Knobs'!$B$15)+(F193*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F193))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G193*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C193+D193+(E193*'03 Mind Knobs'!$B$17)+(F193*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F193))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G193*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K193" t="n">
@@ -54685,7 +55816,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L193" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A193,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B193-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B193))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M193" t="n">
@@ -54727,11 +55858,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I194" t="n">
-        <x:f>--(MIN(1,C194+D194+(E194*'03 Mind Knobs'!$B$15)+(F194*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F194))&gt;=MAX(0.15,0.35+(G194*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C194+D194+(E194*'03 Mind Knobs'!$B$17)+(F194*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F194))&gt;=MAX(0.15,0.35+(G194*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J194" t="n">
-        <x:f>--(MIN(1,C194+D194+(E194*'03 Mind Knobs'!$B$15)+(F194*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F194))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G194*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C194+D194+(E194*'03 Mind Knobs'!$B$17)+(F194*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F194))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G194*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K194" t="n">
@@ -54739,7 +55870,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L194" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A194,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B194-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B194))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M194" t="n">
@@ -54781,11 +55912,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I195" t="n">
-        <x:f>--(MIN(1,C195+D195+(E195*'03 Mind Knobs'!$B$15)+(F195*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F195))&gt;=MAX(0.15,0.35+(G195*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C195+D195+(E195*'03 Mind Knobs'!$B$17)+(F195*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F195))&gt;=MAX(0.15,0.35+(G195*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J195" t="n">
-        <x:f>--(MIN(1,C195+D195+(E195*'03 Mind Knobs'!$B$15)+(F195*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F195))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G195*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C195+D195+(E195*'03 Mind Knobs'!$B$17)+(F195*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F195))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G195*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K195" t="n">
@@ -54793,7 +55924,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L195" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A195,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B195-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B195))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M195" t="n">
@@ -54835,11 +55966,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I196" t="n">
-        <x:f>--(MIN(1,C196+D196+(E196*'03 Mind Knobs'!$B$15)+(F196*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F196))&gt;=MAX(0.15,0.35+(G196*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C196+D196+(E196*'03 Mind Knobs'!$B$17)+(F196*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F196))&gt;=MAX(0.15,0.35+(G196*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J196" t="n">
-        <x:f>--(MIN(1,C196+D196+(E196*'03 Mind Knobs'!$B$15)+(F196*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F196))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G196*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C196+D196+(E196*'03 Mind Knobs'!$B$17)+(F196*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F196))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G196*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K196" t="n">
@@ -54847,7 +55978,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L196" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A196,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B196-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B196))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M196" t="n">
@@ -54889,11 +56020,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I197" t="n">
-        <x:f>--(MIN(1,C197+D197+(E197*'03 Mind Knobs'!$B$15)+(F197*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F197))&gt;=MAX(0.15,0.35+(G197*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C197+D197+(E197*'03 Mind Knobs'!$B$17)+(F197*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F197))&gt;=MAX(0.15,0.35+(G197*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J197" t="n">
-        <x:f>--(MIN(1,C197+D197+(E197*'03 Mind Knobs'!$B$15)+(F197*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F197))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G197*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C197+D197+(E197*'03 Mind Knobs'!$B$17)+(F197*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F197))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G197*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K197" t="n">
@@ -54901,7 +56032,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L197" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A197,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B197-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B197))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M197" t="n">
@@ -54943,11 +56074,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I198" t="n">
-        <x:f>--(MIN(1,C198+D198+(E198*'03 Mind Knobs'!$B$15)+(F198*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F198))&gt;=MAX(0.15,0.35+(G198*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C198+D198+(E198*'03 Mind Knobs'!$B$17)+(F198*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F198))&gt;=MAX(0.15,0.35+(G198*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J198" t="n">
-        <x:f>--(MIN(1,C198+D198+(E198*'03 Mind Knobs'!$B$15)+(F198*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F198))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G198*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C198+D198+(E198*'03 Mind Knobs'!$B$17)+(F198*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F198))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G198*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K198" t="n">
@@ -54955,7 +56086,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L198" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A198,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B198-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B198))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M198" t="n">
@@ -54997,11 +56128,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I199" t="n">
-        <x:f>--(MIN(1,C199+D199+(E199*'03 Mind Knobs'!$B$15)+(F199*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F199))&gt;=MAX(0.15,0.35+(G199*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C199+D199+(E199*'03 Mind Knobs'!$B$17)+(F199*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F199))&gt;=MAX(0.15,0.35+(G199*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J199" t="n">
-        <x:f>--(MIN(1,C199+D199+(E199*'03 Mind Knobs'!$B$15)+(F199*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F199))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G199*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C199+D199+(E199*'03 Mind Knobs'!$B$17)+(F199*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F199))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G199*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K199" t="n">
@@ -55009,7 +56140,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L199" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A199,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B199-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B199))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M199" t="n">
@@ -55051,11 +56182,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I200" t="n">
-        <x:f>--(MIN(1,C200+D200+(E200*'03 Mind Knobs'!$B$15)+(F200*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F200))&gt;=MAX(0.15,0.35+(G200*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C200+D200+(E200*'03 Mind Knobs'!$B$17)+(F200*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F200))&gt;=MAX(0.15,0.35+(G200*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J200" t="n">
-        <x:f>--(MIN(1,C200+D200+(E200*'03 Mind Knobs'!$B$15)+(F200*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F200))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G200*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C200+D200+(E200*'03 Mind Knobs'!$B$17)+(F200*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F200))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G200*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K200" t="n">
@@ -55063,7 +56194,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L200" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A200,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B200-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B200))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M200" t="n">
@@ -55105,11 +56236,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I201" t="n">
-        <x:f>--(MIN(1,C201+D201+(E201*'03 Mind Knobs'!$B$15)+(F201*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F201))&gt;=MAX(0.15,0.35+(G201*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C201+D201+(E201*'03 Mind Knobs'!$B$17)+(F201*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F201))&gt;=MAX(0.15,0.35+(G201*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J201" t="n">
-        <x:f>--(MIN(1,C201+D201+(E201*'03 Mind Knobs'!$B$15)+(F201*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F201))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G201*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C201+D201+(E201*'03 Mind Knobs'!$B$17)+(F201*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F201))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G201*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K201" t="n">
@@ -55117,7 +56248,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L201" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A201,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B201-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B201))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M201" t="n">
@@ -55159,11 +56290,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I202" t="n">
-        <x:f>--(MIN(1,C202+D202+(E202*'03 Mind Knobs'!$B$15)+(F202*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F202))&gt;=MAX(0.15,0.35+(G202*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C202+D202+(E202*'03 Mind Knobs'!$B$17)+(F202*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F202))&gt;=MAX(0.15,0.35+(G202*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J202" t="n">
-        <x:f>--(MIN(1,C202+D202+(E202*'03 Mind Knobs'!$B$15)+(F202*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F202))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G202*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C202+D202+(E202*'03 Mind Knobs'!$B$17)+(F202*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F202))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G202*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K202" t="n">
@@ -55171,7 +56302,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L202" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A202,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B202-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B202))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M202" t="n">
@@ -55213,11 +56344,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I203" t="n">
-        <x:f>--(MIN(1,C203+D203+(E203*'03 Mind Knobs'!$B$15)+(F203*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F203))&gt;=MAX(0.15,0.35+(G203*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C203+D203+(E203*'03 Mind Knobs'!$B$17)+(F203*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F203))&gt;=MAX(0.15,0.35+(G203*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J203" t="n">
-        <x:f>--(MIN(1,C203+D203+(E203*'03 Mind Knobs'!$B$15)+(F203*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F203))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G203*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C203+D203+(E203*'03 Mind Knobs'!$B$17)+(F203*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F203))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G203*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K203" t="n">
@@ -55225,7 +56356,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L203" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A203,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B203-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B203))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M203" t="n">
@@ -55267,11 +56398,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I204" t="n">
-        <x:f>--(MIN(1,C204+D204+(E204*'03 Mind Knobs'!$B$15)+(F204*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F204))&gt;=MAX(0.15,0.35+(G204*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C204+D204+(E204*'03 Mind Knobs'!$B$17)+(F204*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F204))&gt;=MAX(0.15,0.35+(G204*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J204" t="n">
-        <x:f>--(MIN(1,C204+D204+(E204*'03 Mind Knobs'!$B$15)+(F204*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F204))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G204*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C204+D204+(E204*'03 Mind Knobs'!$B$17)+(F204*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F204))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G204*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K204" t="n">
@@ -55279,7 +56410,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L204" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A204,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B204-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B204))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M204" t="n">
@@ -55321,11 +56452,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I205" t="n">
-        <x:f>--(MIN(1,C205+D205+(E205*'03 Mind Knobs'!$B$15)+(F205*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F205))&gt;=MAX(0.15,0.35+(G205*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.15)))</x:f>
+        <x:f>--(MIN(1,C205+D205+(E205*'03 Mind Knobs'!$B$17)+(F205*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F205))&gt;=MAX(0.15,0.35+(G205*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.15)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="J205" t="n">
-        <x:f>--(MIN(1,C205+D205+(E205*'03 Mind Knobs'!$B$15)+(F205*'03 Mind Knobs'!$B$16)+('03 Mind Knobs'!$B$7*F205))&gt;=MIN(0.95,'03 Mind Knobs'!$B$17+(G205*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$11*0.10)))</x:f>
+        <x:f>--(MIN(1,C205+D205+(E205*'03 Mind Knobs'!$B$17)+(F205*'03 Mind Knobs'!$B$18)+('03 Mind Knobs'!$B$7*F205))&gt;=MIN(0.95,'03 Mind Knobs'!$B$19+(G205*'03 Mind Knobs'!$B$10)-('03 Mind Knobs'!$B$13*0.10)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="K205" t="n">
@@ -55333,7 +56464,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L205" t="n">
-        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$14+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$14*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
+        <x:f>--(MAX(SUMIFS('00 Compact View'!$H$6:$H$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$I$6:$I$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$J$6:$J$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$K$6:$K$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205),SUMIFS('00 Compact View'!$L$6:$L$205,'00 Compact View'!$A$6:$A$205,A205,'00 Compact View'!$B$6:$B$205,"&gt;="&amp;B205-'03 Mind Knobs'!$B$16+1,'00 Compact View'!$B$6:$B$205,"&lt;="&amp;B205))&gt;=MAX(1,ROUNDUP('03 Mind Knobs'!$B$16*(1-'03 Mind Knobs'!$B$8),0)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="M205" t="n">
@@ -55354,366 +56485,795 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="4.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="4.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="6.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="6.440000057220459" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="19.5" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="B1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="D1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="E1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="F1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="G1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="H1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="I1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="J1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="K1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
       <x:c r="L1" s="4" t="str">
-        <x:v>06 Mode Presets</x:v>
+        <x:v>06 Habit Efficiency</x:v>
+      </x:c>
+      <x:c r="M1" s="4" t="str">
+        <x:v>06 Habit Efficiency</x:v>
+      </x:c>
+      <x:c r="N1" s="4" t="str">
+        <x:v>06 Habit Efficiency</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="K2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>Global modes set grouped defaults. Mind Knobs can still be edited directly.</x:v>
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="str">
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="str">
+        <x:v>Sample-level trigger + sequence + reward handoff. Outputs stay numeric and inspectable.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="9" t="str">
-        <x:v>id</x:v>
+        <x:v>sample</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>mode</x:v>
+        <x:v>trig</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>nov</x:v>
+        <x:v>seq</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
-        <x:v>em</x:v>
+        <x:v>reward</x:v>
       </x:c>
       <x:c r="E5" s="10" t="str">
-        <x:v>win</x:v>
+        <x:v>loop</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>res</x:v>
+        <x:v>rep</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>cur</x:v>
+        <x:v>conf</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>inner</x:v>
+        <x:v>fail</x:v>
       </x:c>
       <x:c r="I5" s="10" t="str">
-        <x:v>emwin</x:v>
+        <x:v>handoff</x:v>
       </x:c>
       <x:c r="J5" s="10" t="str">
-        <x:v>xw</x:v>
+        <x:v>partial</x:v>
       </x:c>
       <x:c r="K5" s="10" t="str">
-        <x:v>aw</x:v>
-      </x:c>
-      <x:c r="L5" s="11" t="str">
-        <x:v>prom</x:v>
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="L5" s="10" t="str">
+        <x:v>audit</x:v>
+      </x:c>
+      <x:c r="M5" s="10" t="str">
+        <x:v>eff</x:v>
+      </x:c>
+      <x:c r="N5" s="11" t="str">
+        <x:v>safe</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>calm</x:v>
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A6)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A6)*2)/20)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="12" t="n">
-        <x:v>0.3</x:v>
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A6)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A6)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A6)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A6))/40)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="12" t="n">
-        <x:v>0.35</x:v>
+        <x:f>MIN(1,(B6*0.25)+(C6*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.4625</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>12</x:v>
+        <x:f>ROUND(B6*3,0)*100+ROUND(C6*3,0)*10+ROUND(D6*3,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
-        <x:v>0.25</x:v>
+        <x:f>COUNTIF($E$6:$E$15,E6)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G6" s="12" t="n">
-        <x:v>0.35</x:v>
+        <x:f>MIN(1,(D6*0.45)+(MIN(1,F6/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.6414583333333332</x:v>
       </x:c>
       <x:c r="H6" s="12" t="n">
-        <x:v>0.85</x:v>
+        <x:f>MAX(0,(1-D6)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.188125</x:v>
       </x:c>
       <x:c r="I6" s="12" t="n">
-        <x:v>12</x:v>
+        <x:f>--(AND(B6&gt;0,C6&gt;0,D6&gt;=0.45,F6&gt;='03 Mind Knobs'!$B$21,G6&gt;='03 Mind Knobs'!$B$22,H6&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
-        <x:v>0.35</x:v>
+        <x:f>--(AND(I6=0,'03 Mind Knobs'!$B$24=1,B6&gt;0,C6&gt;0,D6&gt;=0.35,G6&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K6" s="12" t="n">
-        <x:v>0.45</x:v>
+        <x:f>--(AND(I6=1,M6&gt;=0.75,N6=1))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L6" s="12" t="n">
-        <x:v>0.65</x:v>
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I6=1,J6=1,K6=1)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G6*0.15)+(I6*0.10)+(J6*0.05))</x:f>
+        <x:v>0.94621875</x:v>
+      </x:c>
+      <x:c r="N6" s="12" t="n">
+        <x:f>--(H6&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="n">
+        <x:f>2</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" t="str">
-        <x:v>curious</x:v>
+      <x:c r="B7" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A7)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A7)*2)/20)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="12" t="n">
-        <x:v>0.7</x:v>
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A7)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A7)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A7)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A7))/40)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:f>MIN(1,(B7*0.25)+(C7*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.4625</x:v>
       </x:c>
       <x:c r="E7" s="12" t="n">
-        <x:v>10</x:v>
+        <x:f>ROUND(B7*3,0)*100+ROUND(C7*3,0)*10+ROUND(D7*3,0)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="12" t="n">
-        <x:v>0.4</x:v>
+        <x:f>COUNTIF($E$6:$E$15,E7)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G7" s="12" t="n">
-        <x:v>0.7</x:v>
+        <x:f>MIN(1,(D7*0.45)+(MIN(1,F7/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.6414583333333332</x:v>
       </x:c>
       <x:c r="H7" s="12" t="n">
-        <x:v>0.8</x:v>
+        <x:f>MAX(0,(1-D7)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.188125</x:v>
       </x:c>
       <x:c r="I7" s="12" t="n">
-        <x:v>10</x:v>
+        <x:f>--(AND(B7&gt;0,C7&gt;0,D7&gt;=0.45,F7&gt;='03 Mind Knobs'!$B$21,G7&gt;='03 Mind Knobs'!$B$22,H7&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:f>--(AND(I7=0,'03 Mind Knobs'!$B$24=1,B7&gt;0,C7&gt;0,D7&gt;=0.35,G7&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="12" t="n">
-        <x:v>0.7</x:v>
+        <x:f>--(AND(I7=1,M7&gt;=0.75,N7=1))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="12" t="n">
-        <x:v>0.55</x:v>
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I7=1,J7=1,K7=1)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G7*0.15)+(I7*0.10)+(J7*0.05))</x:f>
+        <x:v>0.94621875</x:v>
+      </x:c>
+      <x:c r="N7" s="12" t="n">
+        <x:f>--(H7&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="n">
+        <x:f>3</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>focused</x:v>
+      <x:c r="B8" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A8)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A8)*2)/20)</x:f>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="C8" s="12" t="n">
-        <x:v>0.35</x:v>
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A8)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A8)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A8)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A8))/40)</x:f>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="D8" s="12" t="n">
-        <x:v>0.45</x:v>
+        <x:f>MIN(1,(B8*0.25)+(C8*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.525</x:v>
       </x:c>
       <x:c r="E8" s="12" t="n">
-        <x:v>8</x:v>
+        <x:f>ROUND(B8*3,0)*100+ROUND(C8*3,0)*10+ROUND(D8*3,0)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:f>COUNTIF($E$6:$E$15,E8)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="12" t="n">
-        <x:v>0.3</x:v>
+        <x:f>MIN(1,(D8*0.45)+(MIN(1,F8/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.5529166666666667</x:v>
       </x:c>
       <x:c r="H8" s="12" t="n">
-        <x:v>0.9</x:v>
+        <x:f>MAX(0,(1-D8)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.16624999999999998</x:v>
       </x:c>
       <x:c r="I8" s="12" t="n">
-        <x:v>10</x:v>
+        <x:f>--(AND(B8&gt;0,C8&gt;0,D8&gt;=0.45,F8&gt;='03 Mind Knobs'!$B$21,G8&gt;='03 Mind Knobs'!$B$22,H8&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="12" t="n">
-        <x:v>0.4</x:v>
+        <x:f>--(AND(I8=0,'03 Mind Knobs'!$B$24=1,B8&gt;0,C8&gt;0,D8&gt;=0.35,G8&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="12" t="n">
-        <x:v>0.55</x:v>
+        <x:f>--(AND(I8=1,M8&gt;=0.75,N8=1))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L8" s="12" t="n">
-        <x:v>0.6</x:v>
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I8=1,J8=1,K8=1)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G8*0.15)+(I8*0.10)+(J8*0.05))</x:f>
+        <x:v>0.9329375</x:v>
+      </x:c>
+      <x:c r="N8" s="12" t="n">
+        <x:f>--(H8&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="n">
+        <x:f>4</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" t="str">
-        <x:v>strained</x:v>
+      <x:c r="B9" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A9)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A9)*2)/20)</x:f>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="C9" s="12" t="n">
-        <x:v>0.2</x:v>
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A9)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A9)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A9)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A9))/40)</x:f>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D9" s="12" t="n">
-        <x:v>0.55</x:v>
+        <x:f>MIN(1,(B9*0.25)+(C9*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.5875</x:v>
       </x:c>
       <x:c r="E9" s="12" t="n">
-        <x:v>6</x:v>
+        <x:f>ROUND(B9*3,0)*100+ROUND(C9*3,0)*10+ROUND(D9*3,0)</x:f>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F9" s="12" t="n">
-        <x:v>0.8</x:v>
+        <x:f>COUNTIF($E$6:$E$15,E9)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="12" t="n">
-        <x:v>0.15</x:v>
+        <x:f>MIN(1,(D9*0.45)+(MIN(1,F9/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.5810416666666667</x:v>
       </x:c>
       <x:c r="H9" s="12" t="n">
-        <x:v>0.75</x:v>
+        <x:f>MAX(0,(1-D9)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.14437499999999998</x:v>
       </x:c>
       <x:c r="I9" s="12" t="n">
-        <x:v>8</x:v>
+        <x:f>--(AND(B9&gt;0,C9&gt;0,D9&gt;=0.45,F9&gt;='03 Mind Knobs'!$B$21,G9&gt;='03 Mind Knobs'!$B$22,H9&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="12" t="n">
-        <x:v>0.45</x:v>
+        <x:f>--(AND(I9=0,'03 Mind Knobs'!$B$24=1,B9&gt;0,C9&gt;0,D9&gt;=0.35,G9&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K9" s="12" t="n">
-        <x:v>0.45</x:v>
+        <x:f>--(AND(I9=1,M9&gt;=0.75,N9=1))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="12" t="n">
-        <x:v>0.75</x:v>
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I9=1,J9=1,K9=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M9" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G9*0.15)+(I9*0.10)+(J9*0.05))</x:f>
+        <x:v>0.9871562500000001</x:v>
+      </x:c>
+      <x:c r="N9" s="12" t="n">
+        <x:f>--(H9&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="n">
+        <x:f>5</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" t="str">
-        <x:v>danger</x:v>
+      <x:c r="B10" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A10)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A10)*2)/20)</x:f>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="C10" s="12" t="n">
-        <x:v>0.65</x:v>
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A10)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A10)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A10)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A10))/40)</x:f>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="D10" s="12" t="n">
-        <x:v>0.9</x:v>
+        <x:f>MIN(1,(B10*0.25)+(C10*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.5625</x:v>
       </x:c>
       <x:c r="E10" s="12" t="n">
-        <x:v>4</x:v>
+        <x:f>ROUND(B10*3,0)*100+ROUND(C10*3,0)*10+ROUND(D10*3,0)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F10" s="12" t="n">
-        <x:v>0.65</x:v>
+        <x:f>COUNTIF($E$6:$E$15,E10)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="12" t="n">
-        <x:v>0.2</x:v>
+        <x:f>MIN(1,(D10*0.45)+(MIN(1,F10/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.5697916666666667</x:v>
       </x:c>
       <x:c r="H10" s="12" t="n">
-        <x:v>0.45</x:v>
+        <x:f>MAX(0,(1-D10)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.15312499999999998</x:v>
       </x:c>
       <x:c r="I10" s="12" t="n">
-        <x:v>5</x:v>
+        <x:f>--(AND(B10&gt;0,C10&gt;0,D10&gt;=0.45,F10&gt;='03 Mind Knobs'!$B$21,G10&gt;='03 Mind Knobs'!$B$22,H10&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="12" t="n">
-        <x:v>0.75</x:v>
+        <x:f>--(AND(I10=0,'03 Mind Knobs'!$B$24=1,B10&gt;0,C10&gt;0,D10&gt;=0.35,G10&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K10" s="12" t="n">
-        <x:v>0.85</x:v>
+        <x:f>--(AND(I10=1,M10&gt;=0.75,N10=1))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="12" t="n">
-        <x:v>0.45</x:v>
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I10=1,J10=1,K10=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M10" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G10*0.15)+(I10*0.10)+(J10*0.05))</x:f>
+        <x:v>0.98546875</x:v>
+      </x:c>
+      <x:c r="N10" s="12" t="n">
+        <x:f>--(H10&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="n">
+        <x:f>6</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" t="str">
-        <x:v>recovery</x:v>
+      <x:c r="B11" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A11)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A11)*2)/20)</x:f>
+        <x:v>0.35</x:v>
       </x:c>
       <x:c r="C11" s="12" t="n">
-        <x:v>0.25</x:v>
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A11)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A11)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A11)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A11))/40)</x:f>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="D11" s="12" t="n">
+        <x:f>MIN(1,(B11*0.25)+(C11*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.6875</x:v>
+      </x:c>
+      <x:c r="E11" s="12" t="n">
+        <x:f>ROUND(B11*3,0)*100+ROUND(C11*3,0)*10+ROUND(D11*3,0)</x:f>
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="n">
+        <x:f>COUNTIF($E$6:$E$15,E11)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="n">
+        <x:f>MIN(1,(D11*0.45)+(MIN(1,F11/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.6260416666666666</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="n">
+        <x:f>MAX(0,(1-D11)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.109375</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="n">
+        <x:f>--(AND(B11&gt;0,C11&gt;0,D11&gt;=0.45,F11&gt;='03 Mind Knobs'!$B$21,G11&gt;='03 Mind Knobs'!$B$22,H11&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="n">
+        <x:f>--(AND(I11=0,'03 Mind Knobs'!$B$24=1,B11&gt;0,C11&gt;0,D11&gt;=0.35,G11&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="12" t="n">
+        <x:f>--(AND(I11=1,M11&gt;=0.75,N11=1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" s="12" t="n">
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I11=1,J11=1,K11=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M11" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G11*0.15)+(I11*0.10)+(J11*0.05))</x:f>
+        <x:v>0.99390625</x:v>
+      </x:c>
+      <x:c r="N11" s="12" t="n">
+        <x:f>--(H11&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="n">
+        <x:f>7</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A12)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A12)*2)/20)</x:f>
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A12)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A12)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A12)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A12))/40)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="n">
+        <x:f>MIN(1,(B12*0.25)+(C12*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.9500000000000001</x:v>
+      </x:c>
+      <x:c r="E12" s="12" t="n">
+        <x:f>ROUND(B12*3,0)*100+ROUND(C12*3,0)*10+ROUND(D12*3,0)</x:f>
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="n">
+        <x:f>COUNTIF($E$6:$E$15,E12)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="n">
+        <x:f>MIN(1,(D12*0.45)+(MIN(1,F12/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.9775</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="n">
+        <x:f>MAX(0,(1-D12)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.017499999999999974</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="n">
+        <x:f>--(AND(B12&gt;0,C12&gt;0,D12&gt;=0.45,F12&gt;='03 Mind Knobs'!$B$21,G12&gt;='03 Mind Knobs'!$B$22,H12&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="n">
+        <x:f>--(AND(I12=0,'03 Mind Knobs'!$B$24=1,B12&gt;0,C12&gt;0,D12&gt;=0.35,G12&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="12" t="n">
+        <x:f>--(AND(I12=1,M12&gt;=0.75,N12=1))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" s="12" t="n">
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I12=1,J12=1,K12=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M12" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G12*0.15)+(I12*0.10)+(J12*0.05))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N12" s="12" t="n">
+        <x:f>--(H12&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="n">
+        <x:f>8</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A13)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A13)*2)/20)</x:f>
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A13)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A13)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A13)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A13))/40)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="n">
+        <x:f>MIN(1,(B13*0.25)+(C13*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="E13" s="12" t="n">
+        <x:f>ROUND(B13*3,0)*100+ROUND(C13*3,0)*10+ROUND(D13*3,0)</x:f>
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="n">
+        <x:f>COUNTIF($E$6:$E$15,E13)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="n">
+        <x:f>MIN(1,(D13*0.45)+(MIN(1,F13/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.7216666666666667</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="n">
+        <x:f>MAX(0,(1-D13)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.03499999999999999</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="n">
+        <x:f>--(AND(B13&gt;0,C13&gt;0,D13&gt;=0.45,F13&gt;='03 Mind Knobs'!$B$21,G13&gt;='03 Mind Knobs'!$B$22,H13&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="n">
+        <x:f>--(AND(I13=0,'03 Mind Knobs'!$B$24=1,B13&gt;0,C13&gt;0,D13&gt;=0.35,G13&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="12" t="n">
+        <x:f>--(AND(I13=1,M13&gt;=0.75,N13=1))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="12" t="n">
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I13=1,J13=1,K13=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M13" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G13*0.15)+(I13*0.10)+(J13*0.05))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N13" s="12" t="n">
+        <x:f>--(H13&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="n">
+        <x:f>9</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A14)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A14)*2)/20)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A14)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A14)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A14)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A14))/40)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="n">
+        <x:f>MIN(1,(B14*0.25)+(C14*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.9625</x:v>
+      </x:c>
+      <x:c r="E14" s="12" t="n">
+        <x:f>ROUND(B14*3,0)*100+ROUND(C14*3,0)*10+ROUND(D14*3,0)</x:f>
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="n">
+        <x:f>COUNTIF($E$6:$E$15,E14)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="n">
+        <x:f>MIN(1,(D14*0.45)+(MIN(1,F14/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.983125</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="n">
+        <x:f>MAX(0,(1-D14)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.01312499999999999</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="n">
+        <x:f>--(AND(B14&gt;0,C14&gt;0,D14&gt;=0.45,F14&gt;='03 Mind Knobs'!$B$21,G14&gt;='03 Mind Knobs'!$B$22,H14&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="n">
+        <x:f>--(AND(I14=0,'03 Mind Knobs'!$B$24=1,B14&gt;0,C14&gt;0,D14&gt;=0.35,G14&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="12" t="n">
+        <x:f>--(AND(I14=1,M14&gt;=0.75,N14=1))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L14" s="12" t="n">
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I14=1,J14=1,K14=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M14" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G14*0.15)+(I14*0.10)+(J14*0.05))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N14" s="12" t="n">
+        <x:f>--(H14&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="n">
+        <x:f>10</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$V$6:$V$205,'00 Compact View'!$A$6:$A$205,A15)+SUMIFS('00 Compact View'!$Y$6:$Y$205,'00 Compact View'!$A$6:$A$205,A15)*2)/20)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="n">
+        <x:f>MIN(1,(SUMIFS('00 Compact View'!$W$6:$W$205,'00 Compact View'!$A$6:$A$205,A15)+SUMIFS('00 Compact View'!$X$6:$X$205,'00 Compact View'!$A$6:$A$205,A15)+SUMIFS('00 Compact View'!$R$6:$R$205,'00 Compact View'!$A$6:$A$205,A15)+SUMIFS('00 Compact View'!$T$6:$T$205,'00 Compact View'!$A$6:$A$205,A15))/40)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="n">
+        <x:f>MIN(1,(B15*0.25)+(C15*0.25)+('04 Resource Body'!$D$11*0.25)+('04 Resource Body'!$F$11*0.25))</x:f>
+        <x:v>0.9625</x:v>
+      </x:c>
+      <x:c r="E15" s="12" t="n">
+        <x:f>ROUND(B15*3,0)*100+ROUND(C15*3,0)*10+ROUND(D15*3,0)</x:f>
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="n">
+        <x:f>COUNTIF($E$6:$E$15,E15)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="n">
+        <x:f>MIN(1,(D15*0.45)+(MIN(1,F15/'03 Mind Knobs'!$B$21)*0.35)+('04 Resource Body'!$D$11*0.20))</x:f>
+        <x:v>0.983125</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="n">
+        <x:f>MAX(0,(1-D15)*0.35+('04 Resource Body'!$B$10*0.20))</x:f>
+        <x:v>0.01312499999999999</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="n">
+        <x:f>--(AND(B15&gt;0,C15&gt;0,D15&gt;=0.45,F15&gt;='03 Mind Knobs'!$B$21,G15&gt;='03 Mind Knobs'!$B$22,H15&lt;='03 Mind Knobs'!$B$23))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="n">
+        <x:f>--(AND(I15=0,'03 Mind Knobs'!$B$24=1,B15&gt;0,C15&gt;0,D15&gt;=0.35,G15&gt;=('03 Mind Knobs'!$B$22*0.70)))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="12" t="n">
+        <x:f>--(AND(I15=1,M15&gt;=0.75,N15=1))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L15" s="12" t="n">
+        <x:f>--(AND('03 Mind Knobs'!$B$25=1,OR(I15=1,J15=1,K15=1)))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M15" s="12" t="n">
+        <x:f>MIN(1,'04 Resource Body'!$F$11+(G15*0.15)+(I15*0.10)+(J15*0.05))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N15" s="12" t="n">
+        <x:f>--(H15&lt;='03 Mind Knobs'!$B$23)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>avg</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="n">
+        <x:f>AVERAGE(B6:B15)</x:f>
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="n">
+      <x:c r="C16" s="12" t="n">
+        <x:f>AVERAGE(C6:C15)</x:f>
+        <x:v>0.525</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="n">
+        <x:f>AVERAGE(D6:D15)</x:f>
+        <x:v>0.70625</x:v>
+      </x:c>
+      <x:c r="E16" s="12" t="n">
+        <x:f>AVERAGE(E6:E15)</x:f>
+        <x:v>148.2</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="n">
+        <x:f>AVERAGE(F6:F15)</x:f>
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="G16" s="12" t="n">
+        <x:f>AVERAGE(G6:G15)</x:f>
+        <x:v>0.7278125</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="n">
+        <x:f>AVERAGE(H6:H15)</x:f>
+        <x:v>0.1028125</x:v>
+      </x:c>
+      <x:c r="I16" s="12" t="n">
+        <x:f>AVERAGE(I6:I15)</x:f>
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="n">
+        <x:f>AVERAGE(J6:J15)</x:f>
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K16" s="12" t="n">
+        <x:f>AVERAGE(K6:K15)</x:f>
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L16" s="12" t="n">
+        <x:f>AVERAGE(L6:L15)</x:f>
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="n">
-        <x:v>0.88</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="K11" s="12" t="n">
-        <x:v>0.35</x:v>
-      </x:c>
-      <x:c r="L11" s="12" t="n">
-        <x:v>0.8</x:v>
+      <x:c r="M16" s="12" t="n">
+        <x:f>AVERAGE(M6:M15)</x:f>
+        <x:v>0.979190625</x:v>
+      </x:c>
+      <x:c r="N16" s="12" t="n">
+        <x:f>AVERAGE(N6:N15)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:L1"/>
-    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
